--- a/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7076900-84FF-4CCA-89B3-6643B831EC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{58E52DEC-C877-4735-9A21-FAC872A6B544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -886,22 +886,82 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_solelc_spv_022</t>
@@ -916,6 +976,12 @@
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_003</t>
   </si>
   <si>
@@ -928,22 +994,16 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_solelc_spv_020</t>
@@ -958,6 +1018,12 @@
     <t>connecting solar to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
@@ -970,82 +1036,46 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w103653592-380,e_w104239352-380,e_w98421779-380,e_w100952845-380,e_w98427149-380,e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w152597636-380,e_IT9-380,e_w42206116-380,e_IT7-380,e_IT53-380,e_w64200868-380,e_IT30-500</t>
+  </si>
+  <si>
+    <t>e_IT157-380,e_w109993642-380,e_w110310021-380,e_w110330925-380,e_w303965869-380,e_w109588422-380,e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380,e_w107681459-380,e_w107683818-380,e_w41360305-380,e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_IT161-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380,e_w419423704-380,e_IT140-380,e_r13844905-380,e_w891280888-380,e_w60235685-380,e_w1137611914-380,e_w257351439-380,e_w209982720-380,e_w418565264-380,e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380,e_IT93-380,e_w99694910-380,e_w98902899-380,e_w105153431-380</t>
+  </si>
+  <si>
+    <t>e_IT8-380,e_IT7-380,e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w58992998-380,e_w59462263-380,e_w60725875-380,e_w41892273-400,e_w590522266-380</t>
+  </si>
+  <si>
     <t>e_w100113593-380,e_IT135-380,e_r4816679-380</t>
   </si>
   <si>
-    <t>e_w105757794-380,e_w107681459-380,e_w107683818-380,e_w41360305-380,e_w114931087-380</t>
+    <t>e_IT134-380,e_w339703159-380,e_w40634284-380,e_w81931074-380</t>
   </si>
   <si>
     <t>e_w139442467-380,e_w82084013-380,e_IT86-380,e_w81938081-380,e_w155158689-380,e_w59366523-380,e_w158739183-380,e_w81929591-380,e_w100407576-380</t>
@@ -1054,19 +1084,19 @@
     <t>e_IT138-380,e_w74943205-380,e_w143585004-380,e_IT137-380,e_w339706879-380,e_w36873258-380</t>
   </si>
   <si>
+    <t>e_w108020416-380,e_w85196861-380,e_w338790588-380,e_w495354824-380,e_w449694943-380,e_IT154-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w338760116-380,e_w60913666-380</t>
+  </si>
+  <si>
     <t>e_w104359058-380,e_IT116-380,e_w103653592-380</t>
   </si>
   <si>
     <t>e_IT40-500,e_IT30-500,e_w84301904-380,e_w82083756-380,e_w59026315-380</t>
   </si>
   <si>
-    <t>e_w103653592-380,e_w104239352-380,e_w98421779-380,e_w100952845-380,e_w98427149-380,e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w152597636-380,e_IT9-380,e_w42206116-380,e_IT7-380,e_IT53-380,e_w64200868-380,e_IT30-500</t>
-  </si>
-  <si>
-    <t>e_IT157-380,e_w109993642-380,e_w110310021-380,e_w110330925-380,e_w303965869-380,e_w109588422-380,e_w109756016-380</t>
+    <t>e_w743450089-380,e_w1158716725,e_w58931857-380,e_w76709660-380,e_IT137-380,e_w114661587-380,e_w83872215-380,e_w339706878-380,e_w96190189-380,e_w132450233-380,e_w85196861-380,e_w988654143-380</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_w61157826-380,e_w1097982502-380,e_w110138220-380,e_w338753171-380,e_w1117128898-380</t>
   </si>
   <si>
     <t>e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_w76705565-380,e_IT141-380,e_w61712456-380</t>
@@ -1075,43 +1105,103 @@
     <t>e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
   </si>
   <si>
+    <t>e_IT93-380,e_IT71-380,e_IT72-400,e_w72581705-380,e_IT21-380</t>
+  </si>
+  <si>
     <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_w118987056-380</t>
   </si>
   <si>
     <t>e_w100952845-380,e_w107438024-380,e_w236661269-380,e_w105757794-380,e_w116517585-380,e_w211180338-380,e_IT106-380,e_w39255054-380,e_w131291789-380,e_IT108-380,e_w208398923-380,e_w155791516-380</t>
   </si>
   <si>
-    <t>e_w108020416-380,e_w85196861-380,e_w338790588-380,e_w495354824-380,e_w449694943-380,e_IT154-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w338760116-380,e_w60913666-380</t>
-  </si>
-  <si>
-    <t>e_IT134-380,e_w339703159-380,e_w40634284-380,e_w81931074-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380,e_IT71-380,e_IT72-400,e_w72581705-380,e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_IT161-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380,e_w419423704-380,e_IT140-380,e_r13844905-380,e_w891280888-380,e_w60235685-380,e_w1137611914-380,e_w257351439-380,e_w209982720-380,e_w418565264-380,e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w743450089-380,e_w1158716725,e_w58931857-380,e_w76709660-380,e_IT137-380,e_w114661587-380,e_w83872215-380,e_w339706878-380,e_w96190189-380,e_w132450233-380,e_w85196861-380,e_w988654143-380</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_w61157826-380,e_w1097982502-380,e_w110138220-380,e_w338753171-380,e_w1117128898-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380,e_IT93-380,e_w99694910-380,e_w98902899-380,e_w105153431-380</t>
-  </si>
-  <si>
-    <t>e_IT8-380,e_IT7-380,e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_w58992998-380,e_w59462263-380,e_w60725875-380,e_w41892273-400,e_w590522266-380</t>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_wonelc_won_019</t>
@@ -1120,22 +1210,16 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wonelc_won_012</t>
@@ -1144,88 +1228,94 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_r4816679-380,e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_IT141-380</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w40634284-380,e_w81931074-380</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w743450089-380,e_w76705565-380,e_w1158716725,e_w114661587-380,e_w85196861-380</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w105757794-380,e_w107681459-380,e_w41360305-380</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w338753171-380,e_w1117128898-380,e_w110138220-380,e_IT157-380,e_w109993642-380</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w495354824-380,e_w449694943-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w109756016-380,e_w338760116-380,e_w60913666-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w82084013-380,e_w155158689-380,e_w59366523-380,e_w100407576-380,e_w59026315-380,e_w58992998-380,e_w60725875-380</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380,e_IT135-380</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w57384507-380,e_w338753171-380</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w81938081-380,e_w143585004-380,e_w158739183-380,e_w81929591-380,e_w74943205-380</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w60235685-380,e_w1137611914-380,e_w418565264-380,e_w411026199-380</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_IT134-380,e_w339703159-380,e_IT138-380,e_w74943205-380</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w108020416-380,e_w110330925-380</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w339706879-380,e_w36873258-380,e_r13844905-380</t>
   </si>
   <si>
     <t>elc_won_019</t>
@@ -1234,22 +1324,16 @@
     <t>e_w110138220-380,e_w1103579629-380,e_w109993642-380,e_w110310021-380,e_w303965869-380</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_IT134-380,e_w339703159-380,e_IT138-380,e_w74943205-380</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w108020416-380,e_w110330925-380</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w82084013-380,e_w155158689-380,e_w59366523-380,e_w100407576-380,e_w59026315-380,e_w58992998-380,e_w60725875-380</t>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w103653592-380,e_w100952845-380</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_IT161-380,e_w61157826-380,e_w57384507-380,e_w1097982502-380</t>
   </si>
   <si>
     <t>elc_won_012</t>
@@ -1258,88 +1342,40 @@
     <t>e_w988654143-380,e_w891280888-380,e_w257351439-380,e_w209982720-380,e_IT154-380</t>
   </si>
   <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w105757794-380,e_w107681459-380,e_w41360305-380</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w338753171-380,e_w1117128898-380,e_w110138220-380,e_IT157-380,e_w109993642-380</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w495354824-380,e_w449694943-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w109756016-380,e_w338760116-380,e_w60913666-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w339706879-380,e_w36873258-380,e_r13844905-380</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380,e_IT135-380</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w255011550-380,e_w57384507-380,e_w338753171-380</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w81938081-380,e_w143585004-380,e_w158739183-380,e_w81929591-380,e_w74943205-380</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_r4816679-380,e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_IT141-380</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w40634284-380,e_w81931074-380</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w743450089-380,e_w76705565-380,e_w1158716725,e_w114661587-380,e_w85196861-380</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w60235685-380,e_w1137611914-380,e_w418565264-380,e_w411026199-380</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w103653592-380,e_w100952845-380</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_IT161-380,e_w61157826-380,e_w57384507-380,e_w1097982502-380</t>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wofelc_wof_017</t>
@@ -1348,10 +1384,22 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_015</t>
@@ -1366,94 +1414,82 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w303915533-380,e_w203225567,e_w255011550-380,e_IT149-380,e_w118987056-380</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w110138220-380,e_w85196861-380,e_w1103579629-380</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w36873258-380</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w57384507-380</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_w61157826-380,e_w110138220-380</t>
   </si>
   <si>
     <t>elc_wof_017</t>
@@ -1462,10 +1498,19 @@
     <t>e_w57384507-380,e_w338753171-380</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w36873258-380</t>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w199675964-380,e_w109756016-380</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w109756016-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w60888331-380,e_w103386958,e_w145665862-380</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
   </si>
   <si>
     <t>elc_wof_015</t>
@@ -1480,91 +1525,46 @@
     <t>e_w743450089-380,e_w114661587-380</t>
   </si>
   <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w1156702013-380,e_w118987056-380,e_w82767145-380</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w82767145-380,e_w416989699-380,e_r17467354-380,e_w82762493-380</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w105757794-380,e_w414663585-380</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w126203383-380,e_w432729521-380,e_w60913666-380,e_w145665799-380</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_w411026199-380,e_w418565264-380,e_w449694943-380</t>
+  </si>
+  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
     <t>e_w409439916-380,e_w1156702013-380</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w105757794-380,e_w414663585-380</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w126203383-380,e_w432729521-380,e_w60913666-380,e_w145665799-380</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w1156702013-380,e_w118987056-380,e_w82767145-380</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w303915533-380,e_w203225567,e_w255011550-380,e_IT149-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w110138220-380,e_w85196861-380,e_w1103579629-380</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_w411026199-380,e_w418565264-380,e_w449694943-380</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w57384507-380</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_w61157826-380,e_w110138220-380</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w199675964-380,e_w109756016-380</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w109756016-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w60888331-380,e_w103386958,e_w145665862-380</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w82767145-380,e_w416989699-380,e_r17467354-380,e_w82762493-380</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6708,7 +6708,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF8663D-4E5E-4593-8023-8456B766E435}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85F736F7-1212-4AB7-8CFD-7D16BAEFD243}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6946,16 +6946,16 @@
         <v>252</v>
       </c>
       <c r="Y11" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="Z11" t="s">
         <v>304</v>
       </c>
       <c r="AA11">
-        <v>0.99797368969783629</v>
+        <v>0.99860660541325685</v>
       </c>
       <c r="AB11">
-        <v>37.149022206335331</v>
+        <v>25.545567423624604</v>
       </c>
       <c r="AD11" t="s">
         <v>251</v>
@@ -6988,10 +6988,10 @@
         <v>367</v>
       </c>
       <c r="AO11">
-        <v>0.99824223632994047</v>
+        <v>0.99665930146480552</v>
       </c>
       <c r="AP11">
-        <v>32.225667284425562</v>
+        <v>61.246139811898914</v>
       </c>
       <c r="AR11" t="s">
         <v>251</v>
@@ -7024,10 +7024,10 @@
         <v>443</v>
       </c>
       <c r="BC11">
-        <v>0.99386058808473199</v>
+        <v>0.99519711687725765</v>
       </c>
       <c r="BD11">
-        <v>112.55588511324767</v>
+        <v>88.052857250275622</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7092,16 +7092,16 @@
         <v>256</v>
       </c>
       <c r="Y12" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Z12" t="s">
         <v>305</v>
       </c>
       <c r="AA12">
-        <v>0.99839748836760267</v>
+        <v>0.99930680862803622</v>
       </c>
       <c r="AB12">
-        <v>29.37937992728429</v>
+        <v>12.708508486002591</v>
       </c>
       <c r="AD12" t="s">
         <v>251</v>
@@ -7134,10 +7134,10 @@
         <v>369</v>
       </c>
       <c r="AO12">
-        <v>0.99666227090030635</v>
+        <v>0.99833657244056218</v>
       </c>
       <c r="AP12">
-        <v>61.191700161050683</v>
+        <v>30.496171923027788</v>
       </c>
       <c r="AR12" t="s">
         <v>251</v>
@@ -7170,10 +7170,10 @@
         <v>445</v>
       </c>
       <c r="BC12">
-        <v>0.99300217097749499</v>
+        <v>0.99511895269233019</v>
       </c>
       <c r="BD12">
-        <v>128.29353207925857</v>
+        <v>89.485867307280429</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7238,16 +7238,16 @@
         <v>258</v>
       </c>
       <c r="Y13" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="Z13" t="s">
         <v>306</v>
       </c>
       <c r="AA13">
-        <v>0.9992072598548265</v>
+        <v>0.99875191609374314</v>
       </c>
       <c r="AB13">
-        <v>14.533569328180825</v>
+        <v>22.881538281374802</v>
       </c>
       <c r="AD13" t="s">
         <v>251</v>
@@ -7280,10 +7280,10 @@
         <v>371</v>
       </c>
       <c r="AO13">
-        <v>0.99709123993747251</v>
+        <v>0.99791596742605326</v>
       </c>
       <c r="AP13">
-        <v>53.327267813004184</v>
+        <v>38.207263855690094</v>
       </c>
       <c r="AR13" t="s">
         <v>251</v>
@@ -7316,10 +7316,10 @@
         <v>447</v>
       </c>
       <c r="BC13">
-        <v>0.98457979899191617</v>
+        <v>0.99300217097749499</v>
       </c>
       <c r="BD13">
-        <v>282.70368514820279</v>
+        <v>128.29353207925857</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7384,16 +7384,16 @@
         <v>260</v>
       </c>
       <c r="Y14" t="s">
-        <v>248</v>
+        <v>234</v>
       </c>
       <c r="Z14" t="s">
         <v>307</v>
       </c>
       <c r="AA14">
-        <v>0.99803201804692143</v>
+        <v>0.99839748836760267</v>
       </c>
       <c r="AB14">
-        <v>36.079669139774055</v>
+        <v>29.37937992728429</v>
       </c>
       <c r="AD14" t="s">
         <v>251</v>
@@ -7426,10 +7426,10 @@
         <v>373</v>
       </c>
       <c r="AO14">
-        <v>0.99918091147922183</v>
+        <v>0.99876840171930192</v>
       </c>
       <c r="AP14">
-        <v>15.016622880932497</v>
+        <v>22.579301812798484</v>
       </c>
       <c r="AR14" t="s">
         <v>251</v>
@@ -7462,10 +7462,10 @@
         <v>449</v>
       </c>
       <c r="BC14">
-        <v>0.99601718841685227</v>
+        <v>0.9951563190122551</v>
       </c>
       <c r="BD14">
-        <v>73.018212357708393</v>
+        <v>88.800818108657467</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7530,16 +7530,16 @@
         <v>262</v>
       </c>
       <c r="Y15" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="Z15" t="s">
         <v>308</v>
       </c>
       <c r="AA15">
-        <v>0.99736118721915257</v>
+        <v>0.99660728585884595</v>
       </c>
       <c r="AB15">
-        <v>48.378234315535408</v>
+        <v>62.199759254490814</v>
       </c>
       <c r="AD15" t="s">
         <v>251</v>
@@ -7572,10 +7572,10 @@
         <v>375</v>
       </c>
       <c r="AO15">
-        <v>0.9990306565657765</v>
+        <v>0.99845919630435342</v>
       </c>
       <c r="AP15">
-        <v>17.771296294096938</v>
+        <v>28.248067753520438</v>
       </c>
       <c r="AR15" t="s">
         <v>251</v>
@@ -7608,10 +7608,10 @@
         <v>451</v>
       </c>
       <c r="BC15">
-        <v>0.99661535764871823</v>
+        <v>0.98395626279590787</v>
       </c>
       <c r="BD15">
-        <v>62.05177644016608</v>
+        <v>294.13518207502182</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7676,16 +7676,16 @@
         <v>264</v>
       </c>
       <c r="Y16" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="Z16" t="s">
         <v>309</v>
       </c>
       <c r="AA16">
-        <v>0.99856694466146878</v>
+        <v>0.98702432691207775</v>
       </c>
       <c r="AB16">
-        <v>26.272681206405</v>
+        <v>237.88733994524034</v>
       </c>
       <c r="AD16" t="s">
         <v>251</v>
@@ -7718,10 +7718,10 @@
         <v>377</v>
       </c>
       <c r="AO16">
-        <v>0.99845919630435342</v>
+        <v>0.99882321467857593</v>
       </c>
       <c r="AP16">
-        <v>28.248067753520438</v>
+        <v>21.574397559441575</v>
       </c>
       <c r="AR16" t="s">
         <v>251</v>
@@ -7754,10 +7754,10 @@
         <v>453</v>
       </c>
       <c r="BC16">
-        <v>0.99517233046898579</v>
+        <v>0.98404695622985239</v>
       </c>
       <c r="BD16">
-        <v>88.507274735259927</v>
+        <v>292.47246911937344</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7822,16 +7822,16 @@
         <v>266</v>
       </c>
       <c r="Y17" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="Z17" t="s">
         <v>310</v>
       </c>
       <c r="AA17">
-        <v>0.99860660541325685</v>
+        <v>0.99897502886966327</v>
       </c>
       <c r="AB17">
-        <v>25.545567423624604</v>
+        <v>18.791137389507082</v>
       </c>
       <c r="AD17" t="s">
         <v>251</v>
@@ -7864,10 +7864,10 @@
         <v>379</v>
       </c>
       <c r="AO17">
-        <v>0.99882321467857593</v>
+        <v>0.99838829169023302</v>
       </c>
       <c r="AP17">
-        <v>21.574397559441575</v>
+        <v>29.547985679061497</v>
       </c>
       <c r="AR17" t="s">
         <v>251</v>
@@ -7900,10 +7900,10 @@
         <v>455</v>
       </c>
       <c r="BC17">
-        <v>0.99560743175223188</v>
+        <v>0.99386058808473199</v>
       </c>
       <c r="BD17">
-        <v>80.530417875749265</v>
+        <v>112.55588511324767</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7968,16 +7968,16 @@
         <v>268</v>
       </c>
       <c r="Y18" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Z18" t="s">
         <v>311</v>
       </c>
       <c r="AA18">
-        <v>0.99930680862803622</v>
+        <v>0.99877722064413432</v>
       </c>
       <c r="AB18">
-        <v>12.708508486002591</v>
+        <v>22.417621524203621</v>
       </c>
       <c r="AD18" t="s">
         <v>251</v>
@@ -8010,10 +8010,10 @@
         <v>381</v>
       </c>
       <c r="AO18">
-        <v>0.99838829169023302</v>
+        <v>0.99918091147922183</v>
       </c>
       <c r="AP18">
-        <v>29.547985679061497</v>
+        <v>15.016622880932497</v>
       </c>
       <c r="AR18" t="s">
         <v>251</v>
@@ -8046,10 +8046,10 @@
         <v>457</v>
       </c>
       <c r="BC18">
-        <v>0.99135720783404546</v>
+        <v>0.99689089953602861</v>
       </c>
       <c r="BD18">
-        <v>158.45118970916684</v>
+        <v>57.000175172809875</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8114,16 +8114,16 @@
         <v>270</v>
       </c>
       <c r="Y19" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="Z19" t="s">
         <v>312</v>
       </c>
       <c r="AA19">
-        <v>0.99875191609374314</v>
+        <v>0.99600892100673577</v>
       </c>
       <c r="AB19">
-        <v>22.881538281374802</v>
+        <v>73.169781543177265</v>
       </c>
       <c r="AD19" t="s">
         <v>251</v>
@@ -8156,10 +8156,10 @@
         <v>383</v>
       </c>
       <c r="AO19">
-        <v>0.99831790956100308</v>
+        <v>0.99730439376729485</v>
       </c>
       <c r="AP19">
-        <v>30.838324714942974</v>
+        <v>49.419447599594143</v>
       </c>
       <c r="AR19" t="s">
         <v>251</v>
@@ -8192,10 +8192,10 @@
         <v>459</v>
       </c>
       <c r="BC19">
-        <v>0.99519711687725765</v>
+        <v>0.99657569928293988</v>
       </c>
       <c r="BD19">
-        <v>88.052857250275622</v>
+        <v>62.778846479435288</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8260,16 +8260,16 @@
         <v>272</v>
       </c>
       <c r="Y20" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="Z20" t="s">
         <v>313</v>
       </c>
       <c r="AA20">
-        <v>0.99873146688652226</v>
+        <v>0.99886825748232866</v>
       </c>
       <c r="AB20">
-        <v>23.256440413757929</v>
+        <v>20.748612823974995</v>
       </c>
       <c r="AD20" t="s">
         <v>251</v>
@@ -8302,10 +8302,10 @@
         <v>385</v>
       </c>
       <c r="AO20">
-        <v>0.99730439376729485</v>
+        <v>0.99117946235007082</v>
       </c>
       <c r="AP20">
-        <v>49.419447599594143</v>
+        <v>161.7098569153674</v>
       </c>
       <c r="AR20" t="s">
         <v>251</v>
@@ -8335,13 +8335,13 @@
         <v>460</v>
       </c>
       <c r="BB20" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="BC20">
-        <v>0.99511895269233019</v>
+        <v>0.98532533439704995</v>
       </c>
       <c r="BD20">
-        <v>89.485867307280429</v>
+        <v>269.0355360540841</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8406,16 +8406,16 @@
         <v>274</v>
       </c>
       <c r="Y21" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="Z21" t="s">
         <v>314</v>
       </c>
       <c r="AA21">
-        <v>0.99846319033655173</v>
+        <v>0.99797368969783629</v>
       </c>
       <c r="AB21">
-        <v>28.174843829885099</v>
+        <v>37.149022206335331</v>
       </c>
       <c r="AD21" t="s">
         <v>251</v>
@@ -8448,10 +8448,10 @@
         <v>387</v>
       </c>
       <c r="AO21">
-        <v>0.99117946235007082</v>
+        <v>0.99872153620715554</v>
       </c>
       <c r="AP21">
-        <v>161.7098569153674</v>
+        <v>23.438502868816123</v>
       </c>
       <c r="AR21" t="s">
         <v>251</v>
@@ -8478,16 +8478,16 @@
         <v>424</v>
       </c>
       <c r="BA21" t="s">
+        <v>461</v>
+      </c>
+      <c r="BB21" t="s">
         <v>462</v>
       </c>
-      <c r="BB21" t="s">
-        <v>463</v>
-      </c>
       <c r="BC21">
-        <v>0.99706526987313149</v>
+        <v>0.98457979899191617</v>
       </c>
       <c r="BD21">
-        <v>53.8033856592563</v>
+        <v>282.70368514820279</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8552,16 +8552,16 @@
         <v>276</v>
       </c>
       <c r="Y22" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="Z22" t="s">
         <v>315</v>
       </c>
       <c r="AA22">
-        <v>0.99352392397859468</v>
+        <v>0.99749418850407234</v>
       </c>
       <c r="AB22">
-        <v>118.7280603924299</v>
+        <v>45.939877425340249</v>
       </c>
       <c r="AD22" t="s">
         <v>251</v>
@@ -8594,10 +8594,10 @@
         <v>389</v>
       </c>
       <c r="AO22">
-        <v>0.99872153620715554</v>
+        <v>0.99874953222888541</v>
       </c>
       <c r="AP22">
-        <v>23.438502868816123</v>
+        <v>22.925242470433936</v>
       </c>
       <c r="AR22" t="s">
         <v>251</v>
@@ -8624,16 +8624,16 @@
         <v>426</v>
       </c>
       <c r="BA22" t="s">
+        <v>463</v>
+      </c>
+      <c r="BB22" t="s">
         <v>464</v>
       </c>
-      <c r="BB22" t="s">
-        <v>465</v>
-      </c>
       <c r="BC22">
-        <v>0.99447806844329845</v>
+        <v>0.99601718841685227</v>
       </c>
       <c r="BD22">
-        <v>101.23541187286283</v>
+        <v>73.018212357708393</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8698,16 +8698,16 @@
         <v>278</v>
       </c>
       <c r="Y23" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="Z23" t="s">
         <v>316</v>
       </c>
       <c r="AA23">
-        <v>0.99908657148051871</v>
+        <v>0.9992072598548265</v>
       </c>
       <c r="AB23">
-        <v>16.746189523824366</v>
+        <v>14.533569328180825</v>
       </c>
       <c r="AD23" t="s">
         <v>251</v>
@@ -8740,10 +8740,10 @@
         <v>391</v>
       </c>
       <c r="AO23">
-        <v>0.99833657244056218</v>
+        <v>0.99666227090030635</v>
       </c>
       <c r="AP23">
-        <v>30.496171923027788</v>
+        <v>61.191700161050683</v>
       </c>
       <c r="AR23" t="s">
         <v>251</v>
@@ -8770,16 +8770,16 @@
         <v>428</v>
       </c>
       <c r="BA23" t="s">
+        <v>465</v>
+      </c>
+      <c r="BB23" t="s">
         <v>466</v>
       </c>
-      <c r="BB23" t="s">
-        <v>467</v>
-      </c>
       <c r="BC23">
-        <v>0.98532533439704995</v>
+        <v>0.99135720783404546</v>
       </c>
       <c r="BD23">
-        <v>269.0355360540841</v>
+        <v>158.45118970916684</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8844,16 +8844,16 @@
         <v>280</v>
       </c>
       <c r="Y24" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="Z24" t="s">
         <v>317</v>
       </c>
       <c r="AA24">
-        <v>0.99832448937819496</v>
+        <v>0.99803201804692143</v>
       </c>
       <c r="AB24">
-        <v>30.717694733092841</v>
+        <v>36.079669139774055</v>
       </c>
       <c r="AD24" t="s">
         <v>251</v>
@@ -8886,10 +8886,10 @@
         <v>393</v>
       </c>
       <c r="AO24">
-        <v>0.99791596742605326</v>
+        <v>0.99709123993747251</v>
       </c>
       <c r="AP24">
-        <v>38.207263855690094</v>
+        <v>53.327267813004184</v>
       </c>
       <c r="AR24" t="s">
         <v>251</v>
@@ -8916,16 +8916,16 @@
         <v>430</v>
       </c>
       <c r="BA24" t="s">
+        <v>467</v>
+      </c>
+      <c r="BB24" t="s">
         <v>468</v>
       </c>
-      <c r="BB24" t="s">
-        <v>467</v>
-      </c>
       <c r="BC24">
-        <v>0.98395626279590787</v>
+        <v>0.99680123445612556</v>
       </c>
       <c r="BD24">
-        <v>294.13518207502182</v>
+        <v>58.644034971032312</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8990,16 +8990,16 @@
         <v>282</v>
       </c>
       <c r="Y25" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="Z25" t="s">
         <v>318</v>
       </c>
       <c r="AA25">
-        <v>0.99749418850407234</v>
+        <v>0.99832448937819496</v>
       </c>
       <c r="AB25">
-        <v>45.939877425340249</v>
+        <v>30.717694733092841</v>
       </c>
       <c r="AD25" t="s">
         <v>251</v>
@@ -9032,10 +9032,10 @@
         <v>395</v>
       </c>
       <c r="AO25">
-        <v>0.99876840171930192</v>
+        <v>0.99831790956100308</v>
       </c>
       <c r="AP25">
-        <v>22.579301812798484</v>
+        <v>30.838324714942974</v>
       </c>
       <c r="AR25" t="s">
         <v>251</v>
@@ -9068,10 +9068,10 @@
         <v>470</v>
       </c>
       <c r="BC25">
-        <v>0.98404695622985239</v>
+        <v>0.99517233046898579</v>
       </c>
       <c r="BD25">
-        <v>292.47246911937344</v>
+        <v>88.507274735259927</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9136,16 +9136,16 @@
         <v>284</v>
       </c>
       <c r="Y26" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z26" t="s">
         <v>319</v>
       </c>
       <c r="AA26">
-        <v>0.99911795750826049</v>
+        <v>0.99736118721915257</v>
       </c>
       <c r="AB26">
-        <v>16.170779015225147</v>
+        <v>48.378234315535408</v>
       </c>
       <c r="AD26" t="s">
         <v>251</v>
@@ -9178,10 +9178,10 @@
         <v>397</v>
       </c>
       <c r="AO26">
-        <v>0.99874953222888541</v>
+        <v>0.99824223632994047</v>
       </c>
       <c r="AP26">
-        <v>22.925242470433936</v>
+        <v>32.225667284425562</v>
       </c>
       <c r="AR26" t="s">
         <v>251</v>
@@ -9214,10 +9214,10 @@
         <v>472</v>
       </c>
       <c r="BC26">
-        <v>0.99689089953602861</v>
+        <v>0.99560743175223188</v>
       </c>
       <c r="BD26">
-        <v>57.000175172809875</v>
+        <v>80.530417875749265</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9282,16 +9282,16 @@
         <v>286</v>
       </c>
       <c r="Y27" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="Z27" t="s">
         <v>320</v>
       </c>
       <c r="AA27">
-        <v>0.99660728585884595</v>
+        <v>0.99856694466146878</v>
       </c>
       <c r="AB27">
-        <v>62.199759254490814</v>
+        <v>26.272681206405</v>
       </c>
       <c r="AD27" t="s">
         <v>251</v>
@@ -9324,10 +9324,10 @@
         <v>399</v>
       </c>
       <c r="AO27">
-        <v>0.99665930146480552</v>
+        <v>0.99737734269837419</v>
       </c>
       <c r="AP27">
-        <v>61.246139811898914</v>
+        <v>48.082050529806814</v>
       </c>
       <c r="AR27" t="s">
         <v>251</v>
@@ -9360,10 +9360,10 @@
         <v>474</v>
       </c>
       <c r="BC27">
-        <v>0.99657569928293988</v>
+        <v>0.99706526987313149</v>
       </c>
       <c r="BD27">
-        <v>62.778846479435288</v>
+        <v>53.8033856592563</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9428,16 +9428,16 @@
         <v>288</v>
       </c>
       <c r="Y28" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="Z28" t="s">
         <v>321</v>
       </c>
       <c r="AA28">
-        <v>0.98702432691207775</v>
+        <v>0.99837547744095589</v>
       </c>
       <c r="AB28">
-        <v>237.88733994524034</v>
+        <v>29.782913582475086</v>
       </c>
       <c r="AD28" t="s">
         <v>251</v>
@@ -9470,10 +9470,10 @@
         <v>401</v>
       </c>
       <c r="AO28">
-        <v>0.99737734269837419</v>
+        <v>0.99501605983777763</v>
       </c>
       <c r="AP28">
-        <v>48.082050529806814</v>
+        <v>91.372236307409807</v>
       </c>
       <c r="AR28" t="s">
         <v>251</v>
@@ -9506,10 +9506,10 @@
         <v>476</v>
       </c>
       <c r="BC28">
-        <v>0.9951563190122551</v>
+        <v>0.99447806844329845</v>
       </c>
       <c r="BD28">
-        <v>88.800818108657467</v>
+        <v>101.23541187286283</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9574,16 +9574,16 @@
         <v>290</v>
       </c>
       <c r="Y29" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="Z29" t="s">
         <v>322</v>
       </c>
       <c r="AA29">
-        <v>0.99897502886966327</v>
+        <v>0.99748803033916245</v>
       </c>
       <c r="AB29">
-        <v>18.791137389507082</v>
+        <v>46.052777115354985</v>
       </c>
       <c r="AD29" t="s">
         <v>251</v>
@@ -9616,10 +9616,10 @@
         <v>403</v>
       </c>
       <c r="AO29">
-        <v>0.99501605983777763</v>
+        <v>0.9990306565657765</v>
       </c>
       <c r="AP29">
-        <v>91.372236307409807</v>
+        <v>17.771296294096938</v>
       </c>
       <c r="AR29" t="s">
         <v>251</v>
@@ -9652,10 +9652,10 @@
         <v>478</v>
       </c>
       <c r="BC29">
-        <v>0.99680123445612556</v>
+        <v>0.99661535764871823</v>
       </c>
       <c r="BD29">
-        <v>58.644034971032312</v>
+        <v>62.05177644016608</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9720,16 +9720,16 @@
         <v>292</v>
       </c>
       <c r="Y30" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="Z30" t="s">
         <v>323</v>
       </c>
       <c r="AA30">
-        <v>0.99837547744095589</v>
+        <v>0.99873146688652226</v>
       </c>
       <c r="AB30">
-        <v>29.782913582475086</v>
+        <v>23.256440413757929</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9794,16 +9794,16 @@
         <v>294</v>
       </c>
       <c r="Y31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Z31" t="s">
         <v>324</v>
       </c>
       <c r="AA31">
-        <v>0.99748803033916245</v>
+        <v>0.99846319033655173</v>
       </c>
       <c r="AB31">
-        <v>46.052777115354985</v>
+        <v>28.174843829885099</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9868,16 +9868,16 @@
         <v>296</v>
       </c>
       <c r="Y32" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Z32" t="s">
         <v>325</v>
       </c>
       <c r="AA32">
-        <v>0.99877722064413432</v>
+        <v>0.99911795750826049</v>
       </c>
       <c r="AB32">
-        <v>22.417621524203621</v>
+        <v>16.170779015225147</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9942,16 +9942,16 @@
         <v>298</v>
       </c>
       <c r="Y33" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="Z33" t="s">
         <v>326</v>
       </c>
       <c r="AA33">
-        <v>0.99600892100673577</v>
+        <v>0.99352392397859468</v>
       </c>
       <c r="AB33">
-        <v>73.169781543177265</v>
+        <v>118.7280603924299</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -10016,16 +10016,16 @@
         <v>300</v>
       </c>
       <c r="Y34" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="Z34" t="s">
         <v>327</v>
       </c>
       <c r="AA34">
-        <v>0.99886825748232866</v>
+        <v>0.99908657148051871</v>
       </c>
       <c r="AB34">
-        <v>20.748612823974995</v>
+        <v>16.746189523824366</v>
       </c>
     </row>
   </sheetData>
@@ -10034,7 +10034,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B32179C-D3EB-4ACC-81F5-390CAB0BA475}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{554B98DA-9E42-494B-8CE7-A54210F02B5C}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10146,7 +10146,7 @@
         <v>479</v>
       </c>
       <c r="K11" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="L11">
         <v>7.7363165779076795</v>
@@ -10179,7 +10179,7 @@
         <v>517</v>
       </c>
       <c r="X11" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="Y11">
         <v>39.450749999999999</v>
@@ -10214,7 +10214,7 @@
         <v>481</v>
       </c>
       <c r="K12" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="L12">
         <v>2.3427652611420688</v>
@@ -10247,7 +10247,7 @@
         <v>519</v>
       </c>
       <c r="X12" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Y12">
         <v>10.7745</v>
@@ -10282,7 +10282,7 @@
         <v>483</v>
       </c>
       <c r="K13" t="s">
-        <v>390</v>
+        <v>368</v>
       </c>
       <c r="L13">
         <v>21.492626448742886</v>
@@ -10315,7 +10315,7 @@
         <v>521</v>
       </c>
       <c r="X13" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="Y13">
         <v>38.600250000000003</v>
@@ -10350,7 +10350,7 @@
         <v>485</v>
       </c>
       <c r="K14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L14">
         <v>6.3986137173550848</v>
@@ -10383,7 +10383,7 @@
         <v>523</v>
       </c>
       <c r="X14" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="Y14">
         <v>4.0402500000000003</v>
@@ -10418,7 +10418,7 @@
         <v>487</v>
       </c>
       <c r="K15" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="L15">
         <v>4.0537250245901548</v>
@@ -10451,7 +10451,7 @@
         <v>525</v>
       </c>
       <c r="X15" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="Y15">
         <v>39.321750000000002</v>
@@ -10486,7 +10486,7 @@
         <v>489</v>
       </c>
       <c r="K16" t="s">
-        <v>392</v>
+        <v>370</v>
       </c>
       <c r="L16">
         <v>9.6185391844194168</v>
@@ -10519,7 +10519,7 @@
         <v>527</v>
       </c>
       <c r="X16" t="s">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="Y16">
         <v>12.592499999999999</v>
@@ -10554,7 +10554,7 @@
         <v>491</v>
       </c>
       <c r="K17" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="L17">
         <v>20.992062966824207</v>
@@ -10587,7 +10587,7 @@
         <v>529</v>
       </c>
       <c r="X17" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="Y17">
         <v>15.871499999999999</v>
@@ -10622,7 +10622,7 @@
         <v>493</v>
       </c>
       <c r="K18" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="L18">
         <v>4.7225970155809494</v>
@@ -10655,7 +10655,7 @@
         <v>531</v>
       </c>
       <c r="X18" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="Y18">
         <v>19.04175</v>
@@ -10690,7 +10690,7 @@
         <v>495</v>
       </c>
       <c r="K19" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="L19">
         <v>9.0836490896593176</v>
@@ -10723,7 +10723,7 @@
         <v>533</v>
       </c>
       <c r="X19" t="s">
-        <v>475</v>
+        <v>448</v>
       </c>
       <c r="Y19">
         <v>28.344000000000001</v>
@@ -10758,7 +10758,7 @@
         <v>497</v>
       </c>
       <c r="K20" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="L20">
         <v>10.618766499150132</v>
@@ -10791,7 +10791,7 @@
         <v>535</v>
       </c>
       <c r="X20" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
       <c r="Y20">
         <v>14.163</v>
@@ -10826,7 +10826,7 @@
         <v>499</v>
       </c>
       <c r="K21" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L21">
         <v>37.276481001553563</v>
@@ -10859,7 +10859,7 @@
         <v>537</v>
       </c>
       <c r="X21" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="Y21">
         <v>2.0775000000000001</v>
@@ -10894,7 +10894,7 @@
         <v>501</v>
       </c>
       <c r="K22" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="L22">
         <v>20.90644030096918</v>
@@ -10927,7 +10927,7 @@
         <v>539</v>
       </c>
       <c r="X22" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="Y22">
         <v>9.2415000000000003</v>
@@ -10962,7 +10962,7 @@
         <v>503</v>
       </c>
       <c r="K23" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="L23">
         <v>1.24293744829465</v>
@@ -10995,7 +10995,7 @@
         <v>541</v>
       </c>
       <c r="X23" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="Y23">
         <v>0.97650000000000003</v>
@@ -11030,7 +11030,7 @@
         <v>505</v>
       </c>
       <c r="K24" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="L24">
         <v>3.655060122103603</v>
@@ -11063,7 +11063,7 @@
         <v>543</v>
       </c>
       <c r="X24" t="s">
-        <v>469</v>
+        <v>452</v>
       </c>
       <c r="Y24">
         <v>6.8857499999999998</v>
@@ -11098,7 +11098,7 @@
         <v>507</v>
       </c>
       <c r="K25" t="s">
-        <v>398</v>
+        <v>366</v>
       </c>
       <c r="L25">
         <v>48.450394178145253</v>
@@ -11131,7 +11131,7 @@
         <v>545</v>
       </c>
       <c r="X25" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="Y25">
         <v>71.778000000000006</v>
@@ -11166,7 +11166,7 @@
         <v>509</v>
       </c>
       <c r="K26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L26">
         <v>19.948651692996549</v>
@@ -11199,7 +11199,7 @@
         <v>547</v>
       </c>
       <c r="X26" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="Y26">
         <v>40.861499999999999</v>
@@ -11234,7 +11234,7 @@
         <v>511</v>
       </c>
       <c r="K27" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="L27">
         <v>23.13749613808001</v>
@@ -11267,7 +11267,7 @@
         <v>549</v>
       </c>
       <c r="X27" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="Y27">
         <v>53.390250000000002</v>
@@ -11302,7 +11302,7 @@
         <v>513</v>
       </c>
       <c r="K28" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="L28">
         <v>6.7463178806119855</v>
@@ -11335,7 +11335,7 @@
         <v>551</v>
       </c>
       <c r="X28" t="s">
-        <v>468</v>
+        <v>450</v>
       </c>
       <c r="Y28">
         <v>49.423499999999997</v>
@@ -11370,7 +11370,7 @@
         <v>515</v>
       </c>
       <c r="K29" t="s">
-        <v>366</v>
+        <v>396</v>
       </c>
       <c r="L29">
         <v>9.7794224100622564</v>
@@ -11403,7 +11403,7 @@
         <v>553</v>
       </c>
       <c r="X29" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="Y29">
         <v>48.613500000000002</v>
@@ -11418,7 +11418,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A7B2373-35BB-43B2-83A1-9A03E29E8333}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF20497D-26CD-4106-96F8-4BDB8F0C74B5}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13235,7 +13235,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18E4CCF3-E519-4D3A-BFAB-6C949BB321C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{050FDFBC-15BD-4193-A0CD-632D66741D0A}">
   <dimension ref="B2:M15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{58E52DEC-C877-4735-9A21-FAC872A6B544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62EA7BE2-D4A3-4F6F-96A9-3FD2CADB694E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="617">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1977,6 +1977,9 @@
   <si>
     <t>Transformer: e_w74869121-380 → e_w74869121-400</t>
   </si>
+  <si>
+    <t>e_IT10-380,e_IT156-380,e_IT157-380,e_IT158-380,e_IT159-380,e_IT21-380,e_IT42-380,e_IT7-380,e_IT8-380,e_IT9-380,e_IT90-400,e_IT93-380,e_w100113593-380,e_w100407576-380,e_w103381531-380,e_w103653592-380,e_w105757794-380,e_w109588422-380,e_w109756016-380,e_w109993642-380,e_w109997676-380,e_w110138220-380,e_w1103579629-380,e_w110660048-380,e_w1117128898-380,e_w114661587-380,e_w1158716725,e_w118987056-380,e_w143585004-380,e_w145665799-380,e_w145665862-380,e_w146791215-380,e_w149997403-380,e_w155590373-380,e_w157912118-380,e_w158739183-380,e_w172302572-380,e_w199675964-380,e_w203225567,e_w255011550-380,e_w303915533-380,e_w338753171-380,e_w36873258-380,e_w409439916-380,e_w411026199-380,e_w414663585-380,e_w416989699-380,e_w418902800-380,e_w432729521-380,e_w491424937-380,e_w491424937-400,e_w58992998-380,e_w591027058-380,e_w59219335-380,e_w59462715-380,e_w60725875-380,e_w60913666-380,e_w60919237-380,e_w72570378-380,e_w72570474-380,e_w743450089-380,e_w74943205-380,e_w81929591-380,e_w82759380-380,e_w82762493-380,e_w82767145-380,e_w83872215-380</t>
+  </si>
 </sst>
 </file>
 
@@ -1990,7 +1993,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2138,15 +2141,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2238,11 +2234,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2457,7 +2448,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2477,9 +2468,8 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2871,7 +2861,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2891,9 +2880,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="20">
+  <cellStyles count="19">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
-    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3869,7 +3857,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_IT10-380,e_IT156-380,e_IT157-380,e_IT158-380,e_IT159-380,e_IT21-380,e_IT42-380,e_IT7-380,e_IT8-380,e_IT9-380,e_IT90-400,e_IT93-380,e_w100113593-380,e_w100407576-380,e_w103381531-380,e_w103653592-380,e_w105757794-380,e_w109588422-380,e_w109756016-380,e_w109993642-380,e_w109997676-380,e_w110138220-380,e_w1103579629-380,e_w110660048-380,e_w1117128898-380,e_w114661587-380,e_w1158716725,e_w118987056-380,e_w143585004-380,e_w145665799-380,e_w145665862-380,e_w146791215-380,e_w149997403-380,e_w155590373-380,e_w157912118-380,e_w158739183-380,e_w172302572-380,e_w199675964-380,e_w203225567,e_w255011550-380,e_w303915533-380,e_w338753171-380,e_w36873258-380,e_w409439916-380,e_w411026199-380,e_w414663585-380,e_w416989699-380,e_w418902800-380,e_w432729521-380,e_w491424937-380,e_w491424937-400,e_w58992998-380,e_w591027058-380,e_w59219335-380,e_w59462715-380,e_w60725875-380,e_w60913666-380,e_w60919237-380,e_w72570378-380,e_w72570474-380,e_w743450089-380,e_w74943205-380,e_w81929591-380,e_w82759380-380,e_w82762493-380,e_w82767145-380,e_w83872215-380</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -3891,7 +3879,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>ELC</v>
+        <v>e_IT10-380,e_IT156-380,e_IT157-380,e_IT158-380,e_IT159-380,e_IT21-380,e_IT42-380,e_IT7-380,e_IT8-380,e_IT9-380,e_IT90-400,e_IT93-380,e_w100113593-380,e_w100407576-380,e_w103381531-380,e_w103653592-380,e_w105757794-380,e_w109588422-380,e_w109756016-380,e_w109993642-380,e_w109997676-380,e_w110138220-380,e_w1103579629-380,e_w110660048-380,e_w1117128898-380,e_w114661587-380,e_w1158716725,e_w118987056-380,e_w143585004-380,e_w145665799-380,e_w145665862-380,e_w146791215-380,e_w149997403-380,e_w155590373-380,e_w157912118-380,e_w158739183-380,e_w172302572-380,e_w199675964-380,e_w203225567,e_w255011550-380,e_w303915533-380,e_w338753171-380,e_w36873258-380,e_w409439916-380,e_w411026199-380,e_w414663585-380,e_w416989699-380,e_w418902800-380,e_w432729521-380,e_w491424937-380,e_w491424937-400,e_w58992998-380,e_w591027058-380,e_w59219335-380,e_w59462715-380,e_w60725875-380,e_w60913666-380,e_w60919237-380,e_w72570378-380,e_w72570474-380,e_w743450089-380,e_w74943205-380,e_w81929591-380,e_w82759380-380,e_w82762493-380,e_w82767145-380,e_w83872215-380</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -3905,8 +3893,8 @@
       <c r="S28">
         <v>50</v>
       </c>
-      <c r="V28" s="147" t="s">
-        <v>19</v>
+      <c r="V28" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -5452,25 +5440,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="148" t="s">
+      <c r="C1" s="147" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="148"/>
-      <c r="E1" s="148"/>
-      <c r="F1" s="149" t="s">
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="148" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="148"/>
-      <c r="H1" s="150"/>
-      <c r="I1" s="148" t="s">
+      <c r="G1" s="147"/>
+      <c r="H1" s="149"/>
+      <c r="I1" s="147" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="148"/>
-      <c r="N1" s="148"/>
-      <c r="O1" s="151" t="s">
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="150" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5516,7 +5504,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="152"/>
+      <c r="O2" s="151"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5561,7 +5549,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="152"/>
+      <c r="O3" s="151"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5603,7 +5591,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="153"/>
+      <c r="O4" s="152"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>

--- a/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{23AE5C25-D877-4117-8995-5143B6A21938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A6321A7-72E1-4328-A7FF-7D520A9D8FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -889,16 +889,130 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_solelc_spv_021</t>
@@ -925,129 +1039,72 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w108020416-380,e_w85196861-380,e_w338790588-380,e_w495354824-380,e_w449694943-380,e_IT154-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w338760116-380,e_w60913666-380</t>
+  </si>
+  <si>
+    <t>e_w105757794-380,e_w107681459-380,e_w107683818-380,e_w41360305-380,e_w114931087-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_w76705565-380,e_IT141-380,e_w61712456-380</t>
+  </si>
+  <si>
+    <t>e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_IT161-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380,e_w419423704-380,e_IT140-380,e_r13844905-380,e_w891280888-380,e_w60235685-380,e_w1137611914-380,e_w257351439-380,e_w209982720-380,e_w418565264-380,e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_w118987056-380</t>
+  </si>
+  <si>
     <t>e_IT93-380,e_IT71-380,e_IT72-400,e_w72581705-380,e_IT21-380</t>
   </si>
   <si>
+    <t>e_w104359058-380,e_IT93-380,e_w99694910-380,e_w98902899-380,e_w105153431-380</t>
+  </si>
+  <si>
+    <t>e_IT8-380,e_IT7-380,e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w58992998-380,e_w59462263-380,e_w60725875-380,e_w41892273-400,e_w590522266-380</t>
+  </si>
+  <si>
+    <t>e_w100952845-380,e_w107438024-380,e_w236661269-380,e_w105757794-380,e_w116517585-380,e_w211180338-380,e_IT106-380,e_w39255054-380,e_w131291789-380,e_IT108-380,e_w208398923-380,e_w155791516-380</t>
+  </si>
+  <si>
+    <t>e_w103653592-380,e_w104239352-380,e_w98421779-380,e_w100952845-380,e_w98427149-380,e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w152597636-380,e_IT9-380,e_w42206116-380,e_IT7-380,e_IT53-380,e_w64200868-380,e_IT30-500</t>
+  </si>
+  <si>
+    <t>e_IT157-380,e_w109993642-380,e_w110310021-380,e_w110330925-380,e_w303965869-380,e_w109588422-380,e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w100113593-380,e_IT135-380,e_r4816679-380</t>
+  </si>
+  <si>
+    <t>e_IT134-380,e_w339703159-380,e_w40634284-380,e_w81931074-380</t>
+  </si>
+  <si>
+    <t>e_w139442467-380,e_w82084013-380,e_IT86-380,e_w81938081-380,e_w155158689-380,e_w59366523-380,e_w158739183-380,e_w81929591-380,e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_IT138-380,e_w74943205-380,e_w143585004-380,e_IT137-380,e_w339706879-380,e_w36873258-380</t>
+  </si>
+  <si>
     <t>e_w743450089-380,e_w1158716725,e_w58931857-380,e_w76709660-380,e_IT137-380,e_w114661587-380,e_w83872215-380,e_w339706878-380,e_w96190189-380,e_w132450233-380,e_w85196861-380,e_w988654143-380</t>
   </si>
   <si>
@@ -1060,61 +1117,28 @@
     <t>e_IT40-500,e_IT30-500,e_w84301904-380,e_w82083756-380,e_w59026315-380</t>
   </si>
   <si>
-    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_IT161-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380,e_w419423704-380,e_IT140-380,e_r13844905-380,e_w891280888-380,e_w60235685-380,e_w1137611914-380,e_w257351439-380,e_w209982720-380,e_w418565264-380,e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w105757794-380,e_w107681459-380,e_w107683818-380,e_w41360305-380,e_w114931087-380</t>
-  </si>
-  <si>
-    <t>e_w108020416-380,e_w85196861-380,e_w338790588-380,e_w495354824-380,e_w449694943-380,e_IT154-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w338760116-380,e_w60913666-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380,e_w104239352-380,e_w98421779-380,e_w100952845-380,e_w98427149-380,e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w152597636-380,e_IT9-380,e_w42206116-380,e_IT7-380,e_IT53-380,e_w64200868-380,e_IT30-500</t>
-  </si>
-  <si>
-    <t>e_IT157-380,e_w109993642-380,e_w110310021-380,e_w110330925-380,e_w303965869-380,e_w109588422-380,e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w139442467-380,e_w82084013-380,e_IT86-380,e_w81938081-380,e_w155158689-380,e_w59366523-380,e_w158739183-380,e_w81929591-380,e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_IT138-380,e_w74943205-380,e_w143585004-380,e_IT137-380,e_w339706879-380,e_w36873258-380</t>
-  </si>
-  <si>
-    <t>e_w100113593-380,e_IT135-380,e_r4816679-380</t>
-  </si>
-  <si>
-    <t>e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_w76705565-380,e_IT141-380,e_w61712456-380</t>
-  </si>
-  <si>
-    <t>e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_w100952845-380,e_w107438024-380,e_w236661269-380,e_w105757794-380,e_w116517585-380,e_w211180338-380,e_IT106-380,e_w39255054-380,e_w131291789-380,e_IT108-380,e_w208398923-380,e_w155791516-380</t>
-  </si>
-  <si>
-    <t>e_IT134-380,e_w339703159-380,e_w40634284-380,e_w81931074-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380,e_IT93-380,e_w99694910-380,e_w98902899-380,e_w105153431-380</t>
-  </si>
-  <si>
-    <t>e_IT8-380,e_IT7-380,e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_w58992998-380,e_w59462263-380,e_w60725875-380,e_w41892273-400,e_w590522266-380</t>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_002</t>
@@ -1123,112 +1147,112 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_015</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_010</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_008</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w110138220-380,e_w1103579629-380,e_w109993642-380,e_w110310021-380,e_w303965869-380</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_r4816679-380,e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_IT141-380</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w40634284-380,e_w81931074-380</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w743450089-380,e_w76705565-380,e_w1158716725,e_w114661587-380,e_w85196861-380</t>
   </si>
   <si>
     <t>elc_won_002</t>
@@ -1237,112 +1261,124 @@
     <t>e_w100113593-380,e_w414663585-380,e_w416989699-380,e_IT135-380</t>
   </si>
   <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w82084013-380,e_w155158689-380,e_w59366523-380,e_w100407576-380,e_w59026315-380,e_w58992998-380,e_w60725875-380</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w988654143-380,e_w891280888-380,e_w257351439-380,e_w209982720-380,e_IT154-380</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w105757794-380,e_w107681459-380,e_w41360305-380</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_w338753171-380,e_w1117128898-380,e_w110138220-380,e_IT157-380,e_w109993642-380</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_w495354824-380,e_w449694943-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w109756016-380,e_w338760116-380,e_w60913666-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_IT134-380,e_w339703159-380,e_IT138-380,e_w74943205-380</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w108020416-380,e_w110330925-380</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w57384507-380,e_w338753171-380</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w81938081-380,e_w143585004-380,e_w158739183-380,e_w81929591-380,e_w74943205-380</t>
+  </si>
+  <si>
     <t>elc_won_015</t>
   </si>
   <si>
     <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w103653592-380,e_w100952845-380</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_IT161-380,e_w61157826-380,e_w57384507-380,e_w1097982502-380</t>
+  </si>
+  <si>
     <t>elc_won_010</t>
   </si>
   <si>
     <t>e_w60235685-380,e_w1137611914-380,e_w418565264-380,e_w411026199-380</t>
   </si>
   <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w110138220-380,e_w1103579629-380,e_w109993642-380,e_w110310021-380,e_w303965869-380</t>
-  </si>
-  <si>
     <t>elc_won_008</t>
   </si>
   <si>
     <t>e_w339706879-380,e_w36873258-380,e_r13844905-380</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_IT134-380,e_w339703159-380,e_IT138-380,e_w74943205-380</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w108020416-380,e_w110330925-380</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w105757794-380,e_w107681459-380,e_w41360305-380</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_w338753171-380,e_w1117128898-380,e_w110138220-380,e_IT157-380,e_w109993642-380</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_w495354824-380,e_w449694943-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w109756016-380,e_w338760116-380,e_w60913666-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_r4816679-380,e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_IT141-380</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w40634284-380,e_w81931074-380</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w743450089-380,e_w76705565-380,e_w1158716725,e_w114661587-380,e_w85196861-380</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w988654143-380,e_w891280888-380,e_w257351439-380,e_w209982720-380,e_IT154-380</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w82084013-380,e_w155158689-380,e_w59366523-380,e_w100407576-380,e_w59026315-380,e_w58992998-380,e_w60725875-380</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w255011550-380,e_w57384507-380,e_w338753171-380</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w81938081-380,e_w143585004-380,e_w158739183-380,e_w81929591-380,e_w74943205-380</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w103653592-380,e_w100952845-380</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_IT161-380,e_w61157826-380,e_w57384507-380,e_w1097982502-380</t>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wofelc_wof_015</t>
@@ -1357,30 +1393,36 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_019</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_011</t>
   </si>
   <si>
@@ -1393,40 +1435,16 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_004</t>
@@ -1441,22 +1459,40 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w303915533-380,e_w203225567,e_w255011550-380,e_IT149-380,e_w118987056-380</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w110138220-380,e_w85196861-380,e_w1103579629-380</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w409439916-380,e_w1156702013-380</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w36873258-380</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w57384507-380</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_w61157826-380,e_w110138220-380</t>
   </si>
   <si>
     <t>elc_wof_015</t>
@@ -1471,30 +1507,33 @@
     <t>e_w743450089-380,e_w114661587-380</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w82767145-380,e_w416989699-380,e_r17467354-380,e_w82762493-380</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_w338753171-380</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w1156702013-380,e_w118987056-380,e_w82767145-380</t>
+  </si>
+  <si>
     <t>elc_wof_019</t>
   </si>
   <si>
-    <t>e_w57384507-380</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w303915533-380,e_w203225567,e_w255011550-380,e_IT149-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w110138220-380,e_w85196861-380,e_w1103579629-380</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380</t>
-  </si>
-  <si>
     <t>elc_wof_011</t>
   </si>
   <si>
@@ -1507,37 +1546,16 @@
     <t>e_w411026199-380,e_w418565264-380,e_w449694943-380</t>
   </si>
   <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w36873258-380</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w1156702013-380,e_w118987056-380,e_w82767145-380</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_w61157826-380,e_w110138220-380</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_w338753171-380</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w82767145-380,e_w416989699-380,e_r17467354-380,e_w82762493-380</t>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w105757794-380,e_w414663585-380</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w126203383-380,e_w432729521-380,e_w60913666-380,e_w145665799-380</t>
   </si>
   <si>
     <t>elc_wof_004</t>
@@ -1550,24 +1568,6 @@
   </si>
   <si>
     <t>e_w109756016-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w60888331-380,e_w103386958,e_w145665862-380</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w409439916-380,e_w1156702013-380</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w105757794-380,e_w414663585-380</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w126203383-380,e_w432729521-380,e_w60913666-380,e_w145665799-380</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6713,7 +6713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CCCC39E-3E7D-4A03-8F2D-6EE3B75DC4CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F42AB69-7370-4D24-AD74-89E912E57B1E}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6951,16 +6951,16 @@
         <v>253</v>
       </c>
       <c r="Y11" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="Z11" t="s">
         <v>305</v>
       </c>
       <c r="AA11">
-        <v>0.99911795750826049</v>
+        <v>0.99832448937819496</v>
       </c>
       <c r="AB11">
-        <v>16.170779015225147</v>
+        <v>30.717694733092841</v>
       </c>
       <c r="AD11" t="s">
         <v>252</v>
@@ -6993,10 +6993,10 @@
         <v>368</v>
       </c>
       <c r="AO11">
-        <v>0.99730439376729485</v>
+        <v>0.99824223632994047</v>
       </c>
       <c r="AP11">
-        <v>49.419447599594143</v>
+        <v>32.225667284425562</v>
       </c>
       <c r="AR11" t="s">
         <v>252</v>
@@ -7029,10 +7029,10 @@
         <v>444</v>
       </c>
       <c r="BC11">
-        <v>0.98457979899191617</v>
+        <v>0.99519711687725765</v>
       </c>
       <c r="BD11">
-        <v>282.70368514820279</v>
+        <v>88.052857250275622</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7097,16 +7097,16 @@
         <v>257</v>
       </c>
       <c r="Y12" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="Z12" t="s">
         <v>306</v>
       </c>
       <c r="AA12">
-        <v>0.99837547744095589</v>
+        <v>0.99839748836760267</v>
       </c>
       <c r="AB12">
-        <v>29.782913582475086</v>
+        <v>29.37937992728429</v>
       </c>
       <c r="AD12" t="s">
         <v>252</v>
@@ -7139,10 +7139,10 @@
         <v>370</v>
       </c>
       <c r="AO12">
-        <v>0.99665930146480552</v>
+        <v>0.99833657244056218</v>
       </c>
       <c r="AP12">
-        <v>61.246139811898914</v>
+        <v>30.496171923027788</v>
       </c>
       <c r="AR12" t="s">
         <v>252</v>
@@ -7175,10 +7175,10 @@
         <v>446</v>
       </c>
       <c r="BC12">
-        <v>0.99601718841685227</v>
+        <v>0.99511895269233019</v>
       </c>
       <c r="BD12">
-        <v>73.018212357708393</v>
+        <v>89.485867307280429</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7243,16 +7243,16 @@
         <v>259</v>
       </c>
       <c r="Y13" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="Z13" t="s">
         <v>307</v>
       </c>
       <c r="AA13">
-        <v>0.99748803033916245</v>
+        <v>0.99873146688652226</v>
       </c>
       <c r="AB13">
-        <v>46.052777115354985</v>
+        <v>23.256440413757929</v>
       </c>
       <c r="AD13" t="s">
         <v>252</v>
@@ -7285,10 +7285,10 @@
         <v>372</v>
       </c>
       <c r="AO13">
-        <v>0.99874953222888541</v>
+        <v>0.99791596742605326</v>
       </c>
       <c r="AP13">
-        <v>22.925242470433936</v>
+        <v>38.207263855690094</v>
       </c>
       <c r="AR13" t="s">
         <v>252</v>
@@ -7321,10 +7321,10 @@
         <v>448</v>
       </c>
       <c r="BC13">
-        <v>0.98532533439704995</v>
+        <v>0.99661535764871823</v>
       </c>
       <c r="BD13">
-        <v>269.0355360540841</v>
+        <v>62.05177644016608</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7389,16 +7389,16 @@
         <v>261</v>
       </c>
       <c r="Y14" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="Z14" t="s">
         <v>308</v>
       </c>
       <c r="AA14">
-        <v>0.99736118721915257</v>
+        <v>0.99846319033655173</v>
       </c>
       <c r="AB14">
-        <v>48.378234315535408</v>
+        <v>28.174843829885099</v>
       </c>
       <c r="AD14" t="s">
         <v>252</v>
@@ -7431,10 +7431,10 @@
         <v>374</v>
       </c>
       <c r="AO14">
-        <v>0.99824223632994047</v>
+        <v>0.99876840171930192</v>
       </c>
       <c r="AP14">
-        <v>32.225667284425562</v>
+        <v>22.579301812798484</v>
       </c>
       <c r="AR14" t="s">
         <v>252</v>
@@ -7467,10 +7467,10 @@
         <v>450</v>
       </c>
       <c r="BC14">
-        <v>0.99519711687725765</v>
+        <v>0.99300217097749499</v>
       </c>
       <c r="BD14">
-        <v>88.052857250275622</v>
+        <v>128.29353207925857</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7535,16 +7535,16 @@
         <v>263</v>
       </c>
       <c r="Y15" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="Z15" t="s">
         <v>309</v>
       </c>
       <c r="AA15">
-        <v>0.99856694466146878</v>
+        <v>0.99660728585884595</v>
       </c>
       <c r="AB15">
-        <v>26.272681206405</v>
+        <v>62.199759254490814</v>
       </c>
       <c r="AD15" t="s">
         <v>252</v>
@@ -7577,10 +7577,10 @@
         <v>376</v>
       </c>
       <c r="AO15">
-        <v>0.99831790956100308</v>
+        <v>0.99730439376729485</v>
       </c>
       <c r="AP15">
-        <v>30.838324714942974</v>
+        <v>49.419447599594143</v>
       </c>
       <c r="AR15" t="s">
         <v>252</v>
@@ -7613,10 +7613,10 @@
         <v>452</v>
       </c>
       <c r="BC15">
-        <v>0.99511895269233019</v>
+        <v>0.98395626279590787</v>
       </c>
       <c r="BD15">
-        <v>89.485867307280429</v>
+        <v>294.13518207502182</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7681,16 +7681,16 @@
         <v>265</v>
       </c>
       <c r="Y16" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z16" t="s">
         <v>310</v>
       </c>
       <c r="AA16">
-        <v>0.99352392397859468</v>
+        <v>0.98702432691207775</v>
       </c>
       <c r="AB16">
-        <v>118.7280603924299</v>
+        <v>237.88733994524034</v>
       </c>
       <c r="AD16" t="s">
         <v>252</v>
@@ -7723,10 +7723,10 @@
         <v>378</v>
       </c>
       <c r="AO16">
-        <v>0.99666227090030635</v>
+        <v>0.99918091147922183</v>
       </c>
       <c r="AP16">
-        <v>61.191700161050683</v>
+        <v>15.016622880932497</v>
       </c>
       <c r="AR16" t="s">
         <v>252</v>
@@ -7759,10 +7759,10 @@
         <v>454</v>
       </c>
       <c r="BC16">
-        <v>0.9951563190122551</v>
+        <v>0.98404695622985239</v>
       </c>
       <c r="BD16">
-        <v>88.800818108657467</v>
+        <v>292.47246911937344</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7827,16 +7827,16 @@
         <v>267</v>
       </c>
       <c r="Y17" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="Z17" t="s">
         <v>311</v>
       </c>
       <c r="AA17">
-        <v>0.99660728585884595</v>
+        <v>0.99897502886966327</v>
       </c>
       <c r="AB17">
-        <v>62.199759254490814</v>
+        <v>18.791137389507082</v>
       </c>
       <c r="AD17" t="s">
         <v>252</v>
@@ -7869,10 +7869,10 @@
         <v>380</v>
       </c>
       <c r="AO17">
-        <v>0.99709123993747251</v>
+        <v>0.9990306565657765</v>
       </c>
       <c r="AP17">
-        <v>53.327267813004184</v>
+        <v>17.771296294096938</v>
       </c>
       <c r="AR17" t="s">
         <v>252</v>
@@ -7905,10 +7905,10 @@
         <v>456</v>
       </c>
       <c r="BC17">
-        <v>0.99706526987313149</v>
+        <v>0.98457979899191617</v>
       </c>
       <c r="BD17">
-        <v>53.8033856592563</v>
+        <v>282.70368514820279</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7973,16 +7973,16 @@
         <v>269</v>
       </c>
       <c r="Y18" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="Z18" t="s">
         <v>312</v>
       </c>
       <c r="AA18">
-        <v>0.98702432691207775</v>
+        <v>0.99352392397859468</v>
       </c>
       <c r="AB18">
-        <v>237.88733994524034</v>
+        <v>118.7280603924299</v>
       </c>
       <c r="AD18" t="s">
         <v>252</v>
@@ -8051,10 +8051,10 @@
         <v>458</v>
       </c>
       <c r="BC18">
-        <v>0.99447806844329845</v>
+        <v>0.99601718841685227</v>
       </c>
       <c r="BD18">
-        <v>101.23541187286283</v>
+        <v>73.018212357708393</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8119,16 +8119,16 @@
         <v>271</v>
       </c>
       <c r="Y19" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="Z19" t="s">
         <v>313</v>
       </c>
       <c r="AA19">
-        <v>0.99897502886966327</v>
+        <v>0.99911795750826049</v>
       </c>
       <c r="AB19">
-        <v>18.791137389507082</v>
+        <v>16.170779015225147</v>
       </c>
       <c r="AD19" t="s">
         <v>252</v>
@@ -8197,10 +8197,10 @@
         <v>460</v>
       </c>
       <c r="BC19">
-        <v>0.99300217097749499</v>
+        <v>0.99680123445612556</v>
       </c>
       <c r="BD19">
-        <v>128.29353207925857</v>
+        <v>58.644034971032312</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8265,16 +8265,16 @@
         <v>273</v>
       </c>
       <c r="Y20" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="Z20" t="s">
         <v>314</v>
       </c>
       <c r="AA20">
-        <v>0.99839748836760267</v>
+        <v>0.99877722064413432</v>
       </c>
       <c r="AB20">
-        <v>29.37937992728429</v>
+        <v>22.417621524203621</v>
       </c>
       <c r="AD20" t="s">
         <v>252</v>
@@ -8343,10 +8343,10 @@
         <v>462</v>
       </c>
       <c r="BC20">
-        <v>0.99135720783404546</v>
+        <v>0.9951563190122551</v>
       </c>
       <c r="BD20">
-        <v>158.45118970916684</v>
+        <v>88.800818108657467</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8411,16 +8411,16 @@
         <v>275</v>
       </c>
       <c r="Y21" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="Z21" t="s">
         <v>315</v>
       </c>
       <c r="AA21">
-        <v>0.99832448937819496</v>
+        <v>0.99600892100673577</v>
       </c>
       <c r="AB21">
-        <v>30.717694733092841</v>
+        <v>73.169781543177265</v>
       </c>
       <c r="AD21" t="s">
         <v>252</v>
@@ -8453,10 +8453,10 @@
         <v>388</v>
       </c>
       <c r="AO21">
-        <v>0.99833657244056218</v>
+        <v>0.99666227090030635</v>
       </c>
       <c r="AP21">
-        <v>30.496171923027788</v>
+        <v>61.191700161050683</v>
       </c>
       <c r="AR21" t="s">
         <v>252</v>
@@ -8486,13 +8486,13 @@
         <v>463</v>
       </c>
       <c r="BB21" t="s">
-        <v>448</v>
+        <v>464</v>
       </c>
       <c r="BC21">
-        <v>0.98395626279590787</v>
+        <v>0.99386058808473199</v>
       </c>
       <c r="BD21">
-        <v>294.13518207502182</v>
+        <v>112.55588511324767</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8557,16 +8557,16 @@
         <v>277</v>
       </c>
       <c r="Y22" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="Z22" t="s">
         <v>316</v>
       </c>
       <c r="AA22">
-        <v>0.99860660541325685</v>
+        <v>0.99886825748232866</v>
       </c>
       <c r="AB22">
-        <v>25.545567423624604</v>
+        <v>20.748612823974995</v>
       </c>
       <c r="AD22" t="s">
         <v>252</v>
@@ -8599,10 +8599,10 @@
         <v>390</v>
       </c>
       <c r="AO22">
-        <v>0.99791596742605326</v>
+        <v>0.99709123993747251</v>
       </c>
       <c r="AP22">
-        <v>38.207263855690094</v>
+        <v>53.327267813004184</v>
       </c>
       <c r="AR22" t="s">
         <v>252</v>
@@ -8629,16 +8629,16 @@
         <v>427</v>
       </c>
       <c r="BA22" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="BB22" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="BC22">
-        <v>0.98404695622985239</v>
+        <v>0.99135720783404546</v>
       </c>
       <c r="BD22">
-        <v>292.47246911937344</v>
+        <v>158.45118970916684</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8703,16 +8703,16 @@
         <v>279</v>
       </c>
       <c r="Y23" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z23" t="s">
         <v>317</v>
       </c>
       <c r="AA23">
-        <v>0.99930680862803622</v>
+        <v>0.99908657148051871</v>
       </c>
       <c r="AB23">
-        <v>12.708508486002591</v>
+        <v>16.746189523824366</v>
       </c>
       <c r="AD23" t="s">
         <v>252</v>
@@ -8745,10 +8745,10 @@
         <v>392</v>
       </c>
       <c r="AO23">
-        <v>0.99876840171930192</v>
+        <v>0.99117946235007082</v>
       </c>
       <c r="AP23">
-        <v>22.579301812798484</v>
+        <v>161.7098569153674</v>
       </c>
       <c r="AR23" t="s">
         <v>252</v>
@@ -8775,16 +8775,16 @@
         <v>429</v>
       </c>
       <c r="BA23" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="BB23" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="BC23">
-        <v>0.99386058808473199</v>
+        <v>0.98532533439704995</v>
       </c>
       <c r="BD23">
-        <v>112.55588511324767</v>
+        <v>269.0355360540841</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8849,16 +8849,16 @@
         <v>281</v>
       </c>
       <c r="Y24" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="Z24" t="s">
         <v>318</v>
       </c>
       <c r="AA24">
-        <v>0.99875191609374314</v>
+        <v>0.99860660541325685</v>
       </c>
       <c r="AB24">
-        <v>22.881538281374802</v>
+        <v>25.545567423624604</v>
       </c>
       <c r="AD24" t="s">
         <v>252</v>
@@ -8891,10 +8891,10 @@
         <v>394</v>
       </c>
       <c r="AO24">
-        <v>0.9990306565657765</v>
+        <v>0.99872153620715554</v>
       </c>
       <c r="AP24">
-        <v>17.771296294096938</v>
+        <v>23.438502868816123</v>
       </c>
       <c r="AR24" t="s">
         <v>252</v>
@@ -8927,10 +8927,10 @@
         <v>469</v>
       </c>
       <c r="BC24">
-        <v>0.99680123445612556</v>
+        <v>0.99706526987313149</v>
       </c>
       <c r="BD24">
-        <v>58.644034971032312</v>
+        <v>53.8033856592563</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8995,16 +8995,16 @@
         <v>283</v>
       </c>
       <c r="Y25" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="Z25" t="s">
         <v>319</v>
       </c>
       <c r="AA25">
-        <v>0.9992072598548265</v>
+        <v>0.99930680862803622</v>
       </c>
       <c r="AB25">
-        <v>14.533569328180825</v>
+        <v>12.708508486002591</v>
       </c>
       <c r="AD25" t="s">
         <v>252</v>
@@ -9037,10 +9037,10 @@
         <v>396</v>
       </c>
       <c r="AO25">
-        <v>0.99918091147922183</v>
+        <v>0.99665930146480552</v>
       </c>
       <c r="AP25">
-        <v>15.016622880932497</v>
+        <v>61.246139811898914</v>
       </c>
       <c r="AR25" t="s">
         <v>252</v>
@@ -9073,10 +9073,10 @@
         <v>471</v>
       </c>
       <c r="BC25">
-        <v>0.99689089953602861</v>
+        <v>0.99447806844329845</v>
       </c>
       <c r="BD25">
-        <v>57.000175172809875</v>
+        <v>101.23541187286283</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9141,16 +9141,16 @@
         <v>285</v>
       </c>
       <c r="Y26" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="Z26" t="s">
         <v>320</v>
       </c>
       <c r="AA26">
-        <v>0.99803201804692143</v>
+        <v>0.99875191609374314</v>
       </c>
       <c r="AB26">
-        <v>36.079669139774055</v>
+        <v>22.881538281374802</v>
       </c>
       <c r="AD26" t="s">
         <v>252</v>
@@ -9183,10 +9183,10 @@
         <v>398</v>
       </c>
       <c r="AO26">
-        <v>0.99117946235007082</v>
+        <v>0.99737734269837419</v>
       </c>
       <c r="AP26">
-        <v>161.7098569153674</v>
+        <v>48.082050529806814</v>
       </c>
       <c r="AR26" t="s">
         <v>252</v>
@@ -9219,10 +9219,10 @@
         <v>473</v>
       </c>
       <c r="BC26">
-        <v>0.99657569928293988</v>
+        <v>0.99517233046898579</v>
       </c>
       <c r="BD26">
-        <v>62.778846479435288</v>
+        <v>88.507274735259927</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9329,10 +9329,10 @@
         <v>400</v>
       </c>
       <c r="AO27">
-        <v>0.99872153620715554</v>
+        <v>0.99501605983777763</v>
       </c>
       <c r="AP27">
-        <v>23.438502868816123</v>
+        <v>91.372236307409807</v>
       </c>
       <c r="AR27" t="s">
         <v>252</v>
@@ -9365,10 +9365,10 @@
         <v>475</v>
       </c>
       <c r="BC27">
-        <v>0.99661535764871823</v>
+        <v>0.99560743175223188</v>
       </c>
       <c r="BD27">
-        <v>62.05177644016608</v>
+        <v>80.530417875749265</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9433,16 +9433,16 @@
         <v>289</v>
       </c>
       <c r="Y28" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="Z28" t="s">
         <v>322</v>
       </c>
       <c r="AA28">
-        <v>0.99873146688652226</v>
+        <v>0.99749418850407234</v>
       </c>
       <c r="AB28">
-        <v>23.256440413757929</v>
+        <v>45.939877425340249</v>
       </c>
       <c r="AD28" t="s">
         <v>252</v>
@@ -9475,10 +9475,10 @@
         <v>402</v>
       </c>
       <c r="AO28">
-        <v>0.99737734269837419</v>
+        <v>0.99874953222888541</v>
       </c>
       <c r="AP28">
-        <v>48.082050529806814</v>
+        <v>22.925242470433936</v>
       </c>
       <c r="AR28" t="s">
         <v>252</v>
@@ -9511,10 +9511,10 @@
         <v>477</v>
       </c>
       <c r="BC28">
-        <v>0.99517233046898579</v>
+        <v>0.99689089953602861</v>
       </c>
       <c r="BD28">
-        <v>88.507274735259927</v>
+        <v>57.000175172809875</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9579,16 +9579,16 @@
         <v>291</v>
       </c>
       <c r="Y29" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="Z29" t="s">
         <v>323</v>
       </c>
       <c r="AA29">
-        <v>0.99846319033655173</v>
+        <v>0.9992072598548265</v>
       </c>
       <c r="AB29">
-        <v>28.174843829885099</v>
+        <v>14.533569328180825</v>
       </c>
       <c r="AD29" t="s">
         <v>252</v>
@@ -9621,10 +9621,10 @@
         <v>404</v>
       </c>
       <c r="AO29">
-        <v>0.99501605983777763</v>
+        <v>0.99831790956100308</v>
       </c>
       <c r="AP29">
-        <v>91.372236307409807</v>
+        <v>30.838324714942974</v>
       </c>
       <c r="AR29" t="s">
         <v>252</v>
@@ -9657,10 +9657,10 @@
         <v>479</v>
       </c>
       <c r="BC29">
-        <v>0.99560743175223188</v>
+        <v>0.99657569928293988</v>
       </c>
       <c r="BD29">
-        <v>80.530417875749265</v>
+        <v>62.778846479435288</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9725,16 +9725,16 @@
         <v>293</v>
       </c>
       <c r="Y30" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="Z30" t="s">
         <v>324</v>
       </c>
       <c r="AA30">
-        <v>0.99908657148051871</v>
+        <v>0.99803201804692143</v>
       </c>
       <c r="AB30">
-        <v>16.746189523824366</v>
+        <v>36.079669139774055</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9799,16 +9799,16 @@
         <v>295</v>
       </c>
       <c r="Y31" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="Z31" t="s">
         <v>325</v>
       </c>
       <c r="AA31">
-        <v>0.99749418850407234</v>
+        <v>0.99837547744095589</v>
       </c>
       <c r="AB31">
-        <v>45.939877425340249</v>
+        <v>29.782913582475086</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9873,16 +9873,16 @@
         <v>297</v>
       </c>
       <c r="Y32" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="Z32" t="s">
         <v>326</v>
       </c>
       <c r="AA32">
-        <v>0.99877722064413432</v>
+        <v>0.99748803033916245</v>
       </c>
       <c r="AB32">
-        <v>22.417621524203621</v>
+        <v>46.052777115354985</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9947,16 +9947,16 @@
         <v>299</v>
       </c>
       <c r="Y33" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="Z33" t="s">
         <v>327</v>
       </c>
       <c r="AA33">
-        <v>0.99600892100673577</v>
+        <v>0.99736118721915257</v>
       </c>
       <c r="AB33">
-        <v>73.169781543177265</v>
+        <v>48.378234315535408</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -10021,16 +10021,16 @@
         <v>301</v>
       </c>
       <c r="Y34" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z34" t="s">
         <v>328</v>
       </c>
       <c r="AA34">
-        <v>0.99886825748232866</v>
+        <v>0.99856694466146878</v>
       </c>
       <c r="AB34">
-        <v>20.748612823974995</v>
+        <v>26.272681206405</v>
       </c>
     </row>
   </sheetData>
@@ -10039,7 +10039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E02C597-5E84-4549-9366-B256FEDAF5AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40BF757-D049-4810-90CE-90EDE88989C4}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10151,7 +10151,7 @@
         <v>480</v>
       </c>
       <c r="K11" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="L11">
         <v>7.7363165779076795</v>
@@ -10184,7 +10184,7 @@
         <v>518</v>
       </c>
       <c r="X11" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
       <c r="Y11">
         <v>39.450749999999999</v>
@@ -10219,7 +10219,7 @@
         <v>482</v>
       </c>
       <c r="K12" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="L12">
         <v>2.3427652611420688</v>
@@ -10252,7 +10252,7 @@
         <v>520</v>
       </c>
       <c r="X12" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="Y12">
         <v>10.7745</v>
@@ -10287,7 +10287,7 @@
         <v>484</v>
       </c>
       <c r="K13" t="s">
-        <v>387</v>
+        <v>369</v>
       </c>
       <c r="L13">
         <v>21.492626448742886</v>
@@ -10320,7 +10320,7 @@
         <v>522</v>
       </c>
       <c r="X13" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="Y13">
         <v>38.600250000000003</v>
@@ -10355,7 +10355,7 @@
         <v>486</v>
       </c>
       <c r="K14" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="L14">
         <v>6.3986137173550848</v>
@@ -10388,7 +10388,7 @@
         <v>524</v>
       </c>
       <c r="X14" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="Y14">
         <v>4.0402500000000003</v>
@@ -10456,7 +10456,7 @@
         <v>526</v>
       </c>
       <c r="X15" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="Y15">
         <v>39.321750000000002</v>
@@ -10491,7 +10491,7 @@
         <v>490</v>
       </c>
       <c r="K16" t="s">
-        <v>389</v>
+        <v>371</v>
       </c>
       <c r="L16">
         <v>9.6185391844194168</v>
@@ -10524,7 +10524,7 @@
         <v>528</v>
       </c>
       <c r="X16" t="s">
-        <v>474</v>
+        <v>447</v>
       </c>
       <c r="Y16">
         <v>12.592499999999999</v>
@@ -10559,7 +10559,7 @@
         <v>492</v>
       </c>
       <c r="K17" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="L17">
         <v>20.992062966824207</v>
@@ -10592,7 +10592,7 @@
         <v>530</v>
       </c>
       <c r="X17" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="Y17">
         <v>15.871499999999999</v>
@@ -10627,7 +10627,7 @@
         <v>494</v>
       </c>
       <c r="K18" t="s">
-        <v>375</v>
+        <v>403</v>
       </c>
       <c r="L18">
         <v>4.7225970155809494</v>
@@ -10660,7 +10660,7 @@
         <v>532</v>
       </c>
       <c r="X18" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="Y18">
         <v>19.04175</v>
@@ -10695,7 +10695,7 @@
         <v>496</v>
       </c>
       <c r="K19" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="L19">
         <v>9.0836490896593176</v>
@@ -10728,7 +10728,7 @@
         <v>534</v>
       </c>
       <c r="X19" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="Y19">
         <v>28.344000000000001</v>
@@ -10763,7 +10763,7 @@
         <v>498</v>
       </c>
       <c r="K20" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="L20">
         <v>10.618766499150132</v>
@@ -10796,7 +10796,7 @@
         <v>536</v>
       </c>
       <c r="X20" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="Y20">
         <v>14.163</v>
@@ -10864,7 +10864,7 @@
         <v>538</v>
       </c>
       <c r="X21" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="Y21">
         <v>2.0775000000000001</v>
@@ -10899,7 +10899,7 @@
         <v>502</v>
       </c>
       <c r="K22" t="s">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="L22">
         <v>20.90644030096918</v>
@@ -10932,7 +10932,7 @@
         <v>540</v>
       </c>
       <c r="X22" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="Y22">
         <v>9.2415000000000003</v>
@@ -10967,7 +10967,7 @@
         <v>504</v>
       </c>
       <c r="K23" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="L23">
         <v>1.24293744829465</v>
@@ -11000,7 +11000,7 @@
         <v>542</v>
       </c>
       <c r="X23" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="Y23">
         <v>0.97650000000000003</v>
@@ -11035,7 +11035,7 @@
         <v>506</v>
       </c>
       <c r="K24" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="L24">
         <v>3.655060122103603</v>
@@ -11068,7 +11068,7 @@
         <v>544</v>
       </c>
       <c r="X24" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="Y24">
         <v>6.8857499999999998</v>
@@ -11103,7 +11103,7 @@
         <v>508</v>
       </c>
       <c r="K25" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="L25">
         <v>48.450394178145253</v>
@@ -11136,7 +11136,7 @@
         <v>546</v>
       </c>
       <c r="X25" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="Y25">
         <v>71.778000000000006</v>
@@ -11171,7 +11171,7 @@
         <v>510</v>
       </c>
       <c r="K26" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="L26">
         <v>19.948651692996549</v>
@@ -11204,7 +11204,7 @@
         <v>548</v>
       </c>
       <c r="X26" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="Y26">
         <v>40.861499999999999</v>
@@ -11239,7 +11239,7 @@
         <v>512</v>
       </c>
       <c r="K27" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="L27">
         <v>23.13749613808001</v>
@@ -11272,7 +11272,7 @@
         <v>550</v>
       </c>
       <c r="X27" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="Y27">
         <v>53.390250000000002</v>
@@ -11340,7 +11340,7 @@
         <v>552</v>
       </c>
       <c r="X28" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="Y28">
         <v>49.423499999999997</v>
@@ -11375,7 +11375,7 @@
         <v>516</v>
       </c>
       <c r="K29" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="L29">
         <v>9.7794224100622564</v>
@@ -11408,7 +11408,7 @@
         <v>554</v>
       </c>
       <c r="X29" t="s">
-        <v>447</v>
+        <v>467</v>
       </c>
       <c r="Y29">
         <v>48.613500000000002</v>
@@ -11423,7 +11423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C33CB88B-DC27-4B9E-B812-0D44A9E632CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416A00D7-2254-4673-AB4B-76218A5873B7}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13240,7 +13240,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F36A746C-1FDF-44A1-BBF6-CD064E69FBF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825EF5CC-63CB-4693-9676-4491F9A86A3A}">
   <dimension ref="B2:M15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A6321A7-72E1-4328-A7FF-7D520A9D8FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACB7A46E-BF9E-4304-BD9D-9EAA450E975B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -889,16 +889,136 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_016</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 16</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_solelc_spv_009</t>
@@ -907,114 +1027,6 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_021</t>
   </si>
   <si>
@@ -1027,102 +1039,96 @@
     <t>connecting solar to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w103653592-380,e_w104239352-380,e_w98421779-380,e_w100952845-380,e_w98427149-380,e_w162828577-380</t>
+  </si>
+  <si>
+    <t>e_w152597636-380,e_IT9-380,e_w42206116-380,e_IT7-380,e_IT53-380,e_w64200868-380,e_IT30-500</t>
+  </si>
+  <si>
+    <t>e_IT157-380,e_w109993642-380,e_w110310021-380,e_w110330925-380,e_w303965869-380,e_w109588422-380,e_w109756016-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380,e_IT116-380,e_w103653592-380</t>
+  </si>
+  <si>
+    <t>e_IT40-500,e_IT30-500,e_w84301904-380,e_w82083756-380,e_w59026315-380</t>
+  </si>
+  <si>
+    <t>e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_w76705565-380,e_IT141-380,e_w61712456-380</t>
+  </si>
+  <si>
+    <t>e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
+  </si>
+  <si>
+    <t>e_w100952845-380,e_w107438024-380,e_w236661269-380,e_w105757794-380,e_w116517585-380,e_w211180338-380,e_IT106-380,e_w39255054-380,e_w131291789-380,e_IT108-380,e_w208398923-380,e_w155791516-380</t>
+  </si>
+  <si>
+    <t>e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_IT161-380</t>
+  </si>
+  <si>
+    <t>e_w61626687-380,e_w419423704-380,e_IT140-380,e_r13844905-380,e_w891280888-380,e_w60235685-380,e_w1137611914-380,e_w257351439-380,e_w209982720-380,e_w418565264-380,e_w411026199-380</t>
+  </si>
+  <si>
+    <t>e_IT134-380,e_w339703159-380,e_w40634284-380,e_w81931074-380</t>
+  </si>
+  <si>
+    <t>e_w100113593-380,e_IT135-380,e_r4816679-380</t>
+  </si>
+  <si>
+    <t>e_IT93-380,e_IT71-380,e_IT72-400,e_w72581705-380,e_IT21-380</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_w118987056-380</t>
+  </si>
+  <si>
     <t>e_w108020416-380,e_w85196861-380,e_w338790588-380,e_w495354824-380,e_w449694943-380,e_IT154-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w338760116-380,e_w60913666-380</t>
   </si>
   <si>
+    <t>e_w139442467-380,e_w82084013-380,e_IT86-380,e_w81938081-380,e_w155158689-380,e_w59366523-380,e_w158739183-380,e_w81929591-380,e_w100407576-380</t>
+  </si>
+  <si>
+    <t>e_IT138-380,e_w74943205-380,e_w143585004-380,e_IT137-380,e_w339706879-380,e_w36873258-380</t>
+  </si>
+  <si>
+    <t>e_w104359058-380,e_IT93-380,e_w99694910-380,e_w98902899-380,e_w105153431-380</t>
+  </si>
+  <si>
+    <t>e_IT8-380,e_IT7-380,e_w64200868-380</t>
+  </si>
+  <si>
+    <t>e_w58992998-380,e_w59462263-380,e_w60725875-380,e_w41892273-400,e_w590522266-380</t>
+  </si>
+  <si>
     <t>e_w105757794-380,e_w107681459-380,e_w107683818-380,e_w41360305-380,e_w114931087-380</t>
   </si>
   <si>
-    <t>e_w416989699-380,e_r17467354-380,e_w82762493-380,e_w339706880-380,e_w76705565-380,e_IT141-380,e_w61712456-380</t>
-  </si>
-  <si>
-    <t>e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
-  </si>
-  <si>
-    <t>e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_IT161-380</t>
-  </si>
-  <si>
-    <t>e_w61626687-380,e_w419423704-380,e_IT140-380,e_r13844905-380,e_w891280888-380,e_w60235685-380,e_w1137611914-380,e_w257351439-380,e_w209982720-380,e_w418565264-380,e_w411026199-380</t>
-  </si>
-  <si>
-    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>e_IT93-380,e_IT71-380,e_IT72-400,e_w72581705-380,e_IT21-380</t>
-  </si>
-  <si>
-    <t>e_w104359058-380,e_IT93-380,e_w99694910-380,e_w98902899-380,e_w105153431-380</t>
-  </si>
-  <si>
-    <t>e_IT8-380,e_IT7-380,e_w64200868-380</t>
-  </si>
-  <si>
-    <t>e_w58992998-380,e_w59462263-380,e_w60725875-380,e_w41892273-400,e_w590522266-380</t>
-  </si>
-  <si>
-    <t>e_w100952845-380,e_w107438024-380,e_w236661269-380,e_w105757794-380,e_w116517585-380,e_w211180338-380,e_IT106-380,e_w39255054-380,e_w131291789-380,e_IT108-380,e_w208398923-380,e_w155791516-380</t>
-  </si>
-  <si>
-    <t>e_w103653592-380,e_w104239352-380,e_w98421779-380,e_w100952845-380,e_w98427149-380,e_w162828577-380</t>
-  </si>
-  <si>
-    <t>e_w152597636-380,e_IT9-380,e_w42206116-380,e_IT7-380,e_IT53-380,e_w64200868-380,e_IT30-500</t>
-  </si>
-  <si>
-    <t>e_IT157-380,e_w109993642-380,e_w110310021-380,e_w110330925-380,e_w303965869-380,e_w109588422-380,e_w109756016-380</t>
-  </si>
-  <si>
-    <t>e_w100113593-380,e_IT135-380,e_r4816679-380</t>
-  </si>
-  <si>
-    <t>e_IT134-380,e_w339703159-380,e_w40634284-380,e_w81931074-380</t>
-  </si>
-  <si>
-    <t>e_w139442467-380,e_w82084013-380,e_IT86-380,e_w81938081-380,e_w155158689-380,e_w59366523-380,e_w158739183-380,e_w81929591-380,e_w100407576-380</t>
-  </si>
-  <si>
-    <t>e_IT138-380,e_w74943205-380,e_w143585004-380,e_IT137-380,e_w339706879-380,e_w36873258-380</t>
-  </si>
-  <si>
     <t>e_w743450089-380,e_w1158716725,e_w58931857-380,e_w76709660-380,e_IT137-380,e_w114661587-380,e_w83872215-380,e_w339706878-380,e_w96190189-380,e_w132450233-380,e_w85196861-380,e_w988654143-380</t>
   </si>
   <si>
     <t>e_w57384507-380,e_w61157826-380,e_w1097982502-380,e_w110138220-380,e_w338753171-380,e_w1117128898-380</t>
   </si>
   <si>
-    <t>e_w104359058-380,e_IT116-380,e_w103653592-380</t>
-  </si>
-  <si>
-    <t>e_IT40-500,e_IT30-500,e_w84301904-380,e_w82083756-380,e_w59026315-380</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_019</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_003</t>
   </si>
   <si>
@@ -1141,24 +1147,72 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_002</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_005</t>
   </si>
   <si>
@@ -1177,66 +1231,18 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>elc_won_019</t>
   </si>
   <si>
     <t>e_w110138220-380,e_w1103579629-380,e_w109993642-380,e_w110310021-380,e_w303965869-380</t>
   </si>
   <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w988654143-380,e_w891280888-380,e_w257351439-380,e_w209982720-380,e_IT154-380</t>
+  </si>
+  <si>
     <t>elc_won_003</t>
   </si>
   <si>
@@ -1255,24 +1261,72 @@
     <t>e_w743450089-380,e_w76705565-380,e_w1158716725,e_w114661587-380,e_w85196861-380</t>
   </si>
   <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w339706879-380,e_w36873258-380,e_r13844905-380</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w103653592-380,e_w100952845-380</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_IT161-380,e_w61157826-380,e_w57384507-380,e_w1097982502-380</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>e_w82084013-380,e_w155158689-380,e_w59366523-380,e_w100407576-380,e_w59026315-380,e_w58992998-380,e_w60725875-380</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_IT134-380,e_w339703159-380,e_IT138-380,e_w74943205-380</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w108020416-380,e_w110330925-380</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w57384507-380,e_w338753171-380</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w81938081-380,e_w143585004-380,e_w158739183-380,e_w81929591-380,e_w74943205-380</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_w60235685-380,e_w1137611914-380,e_w418565264-380,e_w411026199-380</t>
+  </si>
+  <si>
     <t>elc_won_002</t>
   </si>
   <si>
     <t>e_w100113593-380,e_w414663585-380,e_w416989699-380,e_IT135-380</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>e_w82084013-380,e_w155158689-380,e_w59366523-380,e_w100407576-380,e_w59026315-380,e_w58992998-380,e_w60725875-380</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w988654143-380,e_w891280888-380,e_w257351439-380,e_w209982720-380,e_IT154-380</t>
-  </si>
-  <si>
     <t>elc_won_005</t>
   </si>
   <si>
@@ -1291,58 +1345,64 @@
     <t>e_w495354824-380,e_w449694943-380,e_w1098087457-380,e_w103306951-380,e_w126203383-380,e_w109756016-380,e_w338760116-380,e_w60913666-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w418902800-380,e_w145665799-380</t>
   </si>
   <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_IT134-380,e_w339703159-380,e_IT138-380,e_w74943205-380</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w108020416-380,e_w110330925-380</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_w255011550-380,e_w57384507-380,e_w338753171-380</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w81938081-380,e_w143585004-380,e_w158739183-380,e_w81929591-380,e_w74943205-380</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w255011550-380,e_w303915533-380,e_IT150-380,e_IT149-380,e_w409439916-380,e_w144005863-380,e_w1156702013-380,e_w118987056-380</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w103653592-380,e_w100952845-380</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_IT161-380,e_w61157826-380,e_w57384507-380,e_w1097982502-380</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_w60235685-380,e_w1137611914-380,e_w418565264-380,e_w411026199-380</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w339706879-380,e_w36873258-380,e_r13844905-380</t>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_016</t>
@@ -1357,18 +1417,36 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_002</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_018</t>
   </si>
   <si>
@@ -1381,82 +1459,64 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w105757794-380,e_w414663585-380</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w126203383-380,e_w432729521-380,e_w60913666-380,e_w145665799-380</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_w57384507-380,e_w338753171-380</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_w409439916-380,e_w1156702013-380</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_w199675964-380,e_w109756016-380</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_w109756016-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w60888331-380,e_w103386958,e_w145665862-380</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_w82767145-380,e_w416989699-380,e_r17467354-380,e_w82762493-380</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w103653592-380</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_w411026199-380,e_w418565264-380,e_w449694943-380</t>
   </si>
   <si>
     <t>elc_wof_016</t>
@@ -1471,103 +1531,43 @@
     <t>e_w110138220-380,e_w85196861-380,e_w1103579629-380</t>
   </si>
   <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>e_w409439916-380,e_w1156702013-380</t>
-  </si>
-  <si>
     <t>elc_wof_002</t>
   </si>
   <si>
     <t>e_w36873258-380</t>
   </si>
   <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_w255011550-380,e_w118987056-380,e_w57384507-380</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_w743450089-380,e_w114661587-380</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w57384507-380</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_w1156702013-380,e_w118987056-380,e_w82767145-380</t>
+  </si>
+  <si>
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>e_w57384507-380</t>
-  </si>
-  <si>
     <t>elc_wof_014</t>
   </si>
   <si>
     <t>e_w57384507-380,e_w61157826-380,e_w110138220-380</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w255011550-380,e_w118987056-380,e_w57384507-380</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_w743450089-380,e_w114661587-380</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_w82767145-380,e_w416989699-380,e_r17467354-380,e_w82762493-380</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>e_w100113593-380,e_w414663585-380,e_w416989699-380</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_w57384507-380,e_w338753171-380</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_w1156702013-380,e_w118987056-380,e_w82767145-380</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w103653592-380</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_w411026199-380,e_w418565264-380,e_w449694943-380</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w105757794-380,e_w414663585-380</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w126203383-380,e_w432729521-380,e_w60913666-380,e_w145665799-380</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>e_w199675964-380,e_w109756016-380</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>e_w109756016-380,e_w321724202-380,e_w103381531-380,e_w103386958-380,e_w60888331-380,e_w103386958,e_w145665862-380</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6713,7 +6713,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F42AB69-7370-4D24-AD74-89E912E57B1E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31232554-3211-4E4F-A39A-3B9EFA47EE2E}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6951,16 +6951,16 @@
         <v>253</v>
       </c>
       <c r="Y11" t="s">
-        <v>242</v>
+        <v>228</v>
       </c>
       <c r="Z11" t="s">
         <v>305</v>
       </c>
       <c r="AA11">
-        <v>0.99832448937819496</v>
+        <v>0.99860660541325685</v>
       </c>
       <c r="AB11">
-        <v>30.717694733092841</v>
+        <v>25.545567423624604</v>
       </c>
       <c r="AD11" t="s">
         <v>252</v>
@@ -7029,10 +7029,10 @@
         <v>444</v>
       </c>
       <c r="BC11">
-        <v>0.99519711687725765</v>
+        <v>0.99517233046898579</v>
       </c>
       <c r="BD11">
-        <v>88.052857250275622</v>
+        <v>88.507274735259927</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7097,16 +7097,16 @@
         <v>257</v>
       </c>
       <c r="Y12" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Z12" t="s">
         <v>306</v>
       </c>
       <c r="AA12">
-        <v>0.99839748836760267</v>
+        <v>0.99930680862803622</v>
       </c>
       <c r="AB12">
-        <v>29.37937992728429</v>
+        <v>12.708508486002591</v>
       </c>
       <c r="AD12" t="s">
         <v>252</v>
@@ -7139,10 +7139,10 @@
         <v>370</v>
       </c>
       <c r="AO12">
-        <v>0.99833657244056218</v>
+        <v>0.9990306565657765</v>
       </c>
       <c r="AP12">
-        <v>30.496171923027788</v>
+        <v>17.771296294096938</v>
       </c>
       <c r="AR12" t="s">
         <v>252</v>
@@ -7175,10 +7175,10 @@
         <v>446</v>
       </c>
       <c r="BC12">
-        <v>0.99511895269233019</v>
+        <v>0.99560743175223188</v>
       </c>
       <c r="BD12">
-        <v>89.485867307280429</v>
+        <v>80.530417875749265</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7243,16 +7243,16 @@
         <v>259</v>
       </c>
       <c r="Y13" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="Z13" t="s">
         <v>307</v>
       </c>
       <c r="AA13">
-        <v>0.99873146688652226</v>
+        <v>0.99875191609374314</v>
       </c>
       <c r="AB13">
-        <v>23.256440413757929</v>
+        <v>22.881538281374802</v>
       </c>
       <c r="AD13" t="s">
         <v>252</v>
@@ -7285,10 +7285,10 @@
         <v>372</v>
       </c>
       <c r="AO13">
-        <v>0.99791596742605326</v>
+        <v>0.99833657244056218</v>
       </c>
       <c r="AP13">
-        <v>38.207263855690094</v>
+        <v>30.496171923027788</v>
       </c>
       <c r="AR13" t="s">
         <v>252</v>
@@ -7321,10 +7321,10 @@
         <v>448</v>
       </c>
       <c r="BC13">
-        <v>0.99661535764871823</v>
+        <v>0.99386058808473199</v>
       </c>
       <c r="BD13">
-        <v>62.05177644016608</v>
+        <v>112.55588511324767</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7389,16 +7389,16 @@
         <v>261</v>
       </c>
       <c r="Y14" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="Z14" t="s">
         <v>308</v>
       </c>
       <c r="AA14">
-        <v>0.99846319033655173</v>
+        <v>0.99736118721915257</v>
       </c>
       <c r="AB14">
-        <v>28.174843829885099</v>
+        <v>48.378234315535408</v>
       </c>
       <c r="AD14" t="s">
         <v>252</v>
@@ -7431,10 +7431,10 @@
         <v>374</v>
       </c>
       <c r="AO14">
-        <v>0.99876840171930192</v>
+        <v>0.99791596742605326</v>
       </c>
       <c r="AP14">
-        <v>22.579301812798484</v>
+        <v>38.207263855690094</v>
       </c>
       <c r="AR14" t="s">
         <v>252</v>
@@ -7467,10 +7467,10 @@
         <v>450</v>
       </c>
       <c r="BC14">
-        <v>0.99300217097749499</v>
+        <v>0.99661535764871823</v>
       </c>
       <c r="BD14">
-        <v>128.29353207925857</v>
+        <v>62.05177644016608</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7535,16 +7535,16 @@
         <v>263</v>
       </c>
       <c r="Y15" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="Z15" t="s">
         <v>309</v>
       </c>
       <c r="AA15">
-        <v>0.99660728585884595</v>
+        <v>0.99856694466146878</v>
       </c>
       <c r="AB15">
-        <v>62.199759254490814</v>
+        <v>26.272681206405</v>
       </c>
       <c r="AD15" t="s">
         <v>252</v>
@@ -7577,10 +7577,10 @@
         <v>376</v>
       </c>
       <c r="AO15">
-        <v>0.99730439376729485</v>
+        <v>0.99876840171930192</v>
       </c>
       <c r="AP15">
-        <v>49.419447599594143</v>
+        <v>22.579301812798484</v>
       </c>
       <c r="AR15" t="s">
         <v>252</v>
@@ -7613,10 +7613,10 @@
         <v>452</v>
       </c>
       <c r="BC15">
-        <v>0.98395626279590787</v>
+        <v>0.99689089953602861</v>
       </c>
       <c r="BD15">
-        <v>294.13518207502182</v>
+        <v>57.000175172809875</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7681,16 +7681,16 @@
         <v>265</v>
       </c>
       <c r="Y16" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="Z16" t="s">
         <v>310</v>
       </c>
       <c r="AA16">
-        <v>0.98702432691207775</v>
+        <v>0.99873146688652226</v>
       </c>
       <c r="AB16">
-        <v>237.88733994524034</v>
+        <v>23.256440413757929</v>
       </c>
       <c r="AD16" t="s">
         <v>252</v>
@@ -7723,10 +7723,10 @@
         <v>378</v>
       </c>
       <c r="AO16">
-        <v>0.99918091147922183</v>
+        <v>0.99831790956100308</v>
       </c>
       <c r="AP16">
-        <v>15.016622880932497</v>
+        <v>30.838324714942974</v>
       </c>
       <c r="AR16" t="s">
         <v>252</v>
@@ -7759,10 +7759,10 @@
         <v>454</v>
       </c>
       <c r="BC16">
-        <v>0.98404695622985239</v>
+        <v>0.99657569928293988</v>
       </c>
       <c r="BD16">
-        <v>292.47246911937344</v>
+        <v>62.778846479435288</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7827,16 +7827,16 @@
         <v>267</v>
       </c>
       <c r="Y17" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z17" t="s">
         <v>311</v>
       </c>
       <c r="AA17">
-        <v>0.99897502886966327</v>
+        <v>0.99846319033655173</v>
       </c>
       <c r="AB17">
-        <v>18.791137389507082</v>
+        <v>28.174843829885099</v>
       </c>
       <c r="AD17" t="s">
         <v>252</v>
@@ -7869,10 +7869,10 @@
         <v>380</v>
       </c>
       <c r="AO17">
-        <v>0.9990306565657765</v>
+        <v>0.99665930146480552</v>
       </c>
       <c r="AP17">
-        <v>17.771296294096938</v>
+        <v>61.246139811898914</v>
       </c>
       <c r="AR17" t="s">
         <v>252</v>
@@ -7905,10 +7905,10 @@
         <v>456</v>
       </c>
       <c r="BC17">
-        <v>0.98457979899191617</v>
+        <v>0.99680123445612556</v>
       </c>
       <c r="BD17">
-        <v>282.70368514820279</v>
+        <v>58.644034971032312</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7973,16 +7973,16 @@
         <v>269</v>
       </c>
       <c r="Y18" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="Z18" t="s">
         <v>312</v>
       </c>
       <c r="AA18">
-        <v>0.99352392397859468</v>
+        <v>0.99908657148051871</v>
       </c>
       <c r="AB18">
-        <v>118.7280603924299</v>
+        <v>16.746189523824366</v>
       </c>
       <c r="AD18" t="s">
         <v>252</v>
@@ -8015,10 +8015,10 @@
         <v>382</v>
       </c>
       <c r="AO18">
-        <v>0.99845919630435342</v>
+        <v>0.99737734269837419</v>
       </c>
       <c r="AP18">
-        <v>28.248067753520438</v>
+        <v>48.082050529806814</v>
       </c>
       <c r="AR18" t="s">
         <v>252</v>
@@ -8051,10 +8051,10 @@
         <v>458</v>
       </c>
       <c r="BC18">
-        <v>0.99601718841685227</v>
+        <v>0.9951563190122551</v>
       </c>
       <c r="BD18">
-        <v>73.018212357708393</v>
+        <v>88.800818108657467</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8119,16 +8119,16 @@
         <v>271</v>
       </c>
       <c r="Y19" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="Z19" t="s">
         <v>313</v>
       </c>
       <c r="AA19">
-        <v>0.99911795750826049</v>
+        <v>0.99660728585884595</v>
       </c>
       <c r="AB19">
-        <v>16.170779015225147</v>
+        <v>62.199759254490814</v>
       </c>
       <c r="AD19" t="s">
         <v>252</v>
@@ -8161,10 +8161,10 @@
         <v>384</v>
       </c>
       <c r="AO19">
-        <v>0.99882321467857593</v>
+        <v>0.99501605983777763</v>
       </c>
       <c r="AP19">
-        <v>21.574397559441575</v>
+        <v>91.372236307409807</v>
       </c>
       <c r="AR19" t="s">
         <v>252</v>
@@ -8197,10 +8197,10 @@
         <v>460</v>
       </c>
       <c r="BC19">
-        <v>0.99680123445612556</v>
+        <v>0.99706526987313149</v>
       </c>
       <c r="BD19">
-        <v>58.644034971032312</v>
+        <v>53.8033856592563</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8265,16 +8265,16 @@
         <v>273</v>
       </c>
       <c r="Y20" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="Z20" t="s">
         <v>314</v>
       </c>
       <c r="AA20">
-        <v>0.99877722064413432</v>
+        <v>0.98702432691207775</v>
       </c>
       <c r="AB20">
-        <v>22.417621524203621</v>
+        <v>237.88733994524034</v>
       </c>
       <c r="AD20" t="s">
         <v>252</v>
@@ -8307,10 +8307,10 @@
         <v>386</v>
       </c>
       <c r="AO20">
-        <v>0.99838829169023302</v>
+        <v>0.99918091147922183</v>
       </c>
       <c r="AP20">
-        <v>29.547985679061497</v>
+        <v>15.016622880932497</v>
       </c>
       <c r="AR20" t="s">
         <v>252</v>
@@ -8343,10 +8343,10 @@
         <v>462</v>
       </c>
       <c r="BC20">
-        <v>0.9951563190122551</v>
+        <v>0.99447806844329845</v>
       </c>
       <c r="BD20">
-        <v>88.800818108657467</v>
+        <v>101.23541187286283</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8411,16 +8411,16 @@
         <v>275</v>
       </c>
       <c r="Y21" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="Z21" t="s">
         <v>315</v>
       </c>
       <c r="AA21">
-        <v>0.99600892100673577</v>
+        <v>0.99897502886966327</v>
       </c>
       <c r="AB21">
-        <v>73.169781543177265</v>
+        <v>18.791137389507082</v>
       </c>
       <c r="AD21" t="s">
         <v>252</v>
@@ -8489,10 +8489,10 @@
         <v>464</v>
       </c>
       <c r="BC21">
-        <v>0.99386058808473199</v>
+        <v>0.99519711687725765</v>
       </c>
       <c r="BD21">
-        <v>112.55588511324767</v>
+        <v>88.052857250275622</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8557,16 +8557,16 @@
         <v>277</v>
       </c>
       <c r="Y22" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="Z22" t="s">
         <v>316</v>
       </c>
       <c r="AA22">
-        <v>0.99886825748232866</v>
+        <v>0.99749418850407234</v>
       </c>
       <c r="AB22">
-        <v>20.748612823974995</v>
+        <v>45.939877425340249</v>
       </c>
       <c r="AD22" t="s">
         <v>252</v>
@@ -8635,10 +8635,10 @@
         <v>466</v>
       </c>
       <c r="BC22">
-        <v>0.99135720783404546</v>
+        <v>0.99511895269233019</v>
       </c>
       <c r="BD22">
-        <v>158.45118970916684</v>
+        <v>89.485867307280429</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8703,16 +8703,16 @@
         <v>279</v>
       </c>
       <c r="Y23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s">
         <v>317</v>
       </c>
       <c r="AA23">
-        <v>0.99908657148051871</v>
+        <v>0.99797368969783629</v>
       </c>
       <c r="AB23">
-        <v>16.746189523824366</v>
+        <v>37.149022206335331</v>
       </c>
       <c r="AD23" t="s">
         <v>252</v>
@@ -8778,13 +8778,13 @@
         <v>467</v>
       </c>
       <c r="BB23" t="s">
-        <v>452</v>
+        <v>468</v>
       </c>
       <c r="BC23">
-        <v>0.98532533439704995</v>
+        <v>0.99300217097749499</v>
       </c>
       <c r="BD23">
-        <v>269.0355360540841</v>
+        <v>128.29353207925857</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8849,16 +8849,16 @@
         <v>281</v>
       </c>
       <c r="Y24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Z24" t="s">
         <v>318</v>
       </c>
       <c r="AA24">
-        <v>0.99860660541325685</v>
+        <v>0.99911795750826049</v>
       </c>
       <c r="AB24">
-        <v>25.545567423624604</v>
+        <v>16.170779015225147</v>
       </c>
       <c r="AD24" t="s">
         <v>252</v>
@@ -8921,16 +8921,16 @@
         <v>431</v>
       </c>
       <c r="BA24" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="BB24" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="BC24">
-        <v>0.99706526987313149</v>
+        <v>0.98457979899191617</v>
       </c>
       <c r="BD24">
-        <v>53.8033856592563</v>
+        <v>282.70368514820279</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8995,16 +8995,16 @@
         <v>283</v>
       </c>
       <c r="Y25" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="Z25" t="s">
         <v>319</v>
       </c>
       <c r="AA25">
-        <v>0.99930680862803622</v>
+        <v>0.99352392397859468</v>
       </c>
       <c r="AB25">
-        <v>12.708508486002591</v>
+        <v>118.7280603924299</v>
       </c>
       <c r="AD25" t="s">
         <v>252</v>
@@ -9037,10 +9037,10 @@
         <v>396</v>
       </c>
       <c r="AO25">
-        <v>0.99665930146480552</v>
+        <v>0.99874953222888541</v>
       </c>
       <c r="AP25">
-        <v>61.246139811898914</v>
+        <v>22.925242470433936</v>
       </c>
       <c r="AR25" t="s">
         <v>252</v>
@@ -9067,16 +9067,16 @@
         <v>433</v>
       </c>
       <c r="BA25" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="BB25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="BC25">
-        <v>0.99447806844329845</v>
+        <v>0.99601718841685227</v>
       </c>
       <c r="BD25">
-        <v>101.23541187286283</v>
+        <v>73.018212357708393</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9141,16 +9141,16 @@
         <v>285</v>
       </c>
       <c r="Y26" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Z26" t="s">
         <v>320</v>
       </c>
       <c r="AA26">
-        <v>0.99875191609374314</v>
+        <v>0.99832448937819496</v>
       </c>
       <c r="AB26">
-        <v>22.881538281374802</v>
+        <v>30.717694733092841</v>
       </c>
       <c r="AD26" t="s">
         <v>252</v>
@@ -9183,10 +9183,10 @@
         <v>398</v>
       </c>
       <c r="AO26">
-        <v>0.99737734269837419</v>
+        <v>0.99730439376729485</v>
       </c>
       <c r="AP26">
-        <v>48.082050529806814</v>
+        <v>49.419447599594143</v>
       </c>
       <c r="AR26" t="s">
         <v>252</v>
@@ -9213,16 +9213,16 @@
         <v>435</v>
       </c>
       <c r="BA26" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="BB26" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="BC26">
-        <v>0.99517233046898579</v>
+        <v>0.98532533439704995</v>
       </c>
       <c r="BD26">
-        <v>88.507274735259927</v>
+        <v>269.0355360540841</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9287,16 +9287,16 @@
         <v>287</v>
       </c>
       <c r="Y27" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="Z27" t="s">
         <v>321</v>
       </c>
       <c r="AA27">
-        <v>0.99797368969783629</v>
+        <v>0.9992072598548265</v>
       </c>
       <c r="AB27">
-        <v>37.149022206335331</v>
+        <v>14.533569328180825</v>
       </c>
       <c r="AD27" t="s">
         <v>252</v>
@@ -9329,10 +9329,10 @@
         <v>400</v>
       </c>
       <c r="AO27">
-        <v>0.99501605983777763</v>
+        <v>0.99845919630435342</v>
       </c>
       <c r="AP27">
-        <v>91.372236307409807</v>
+        <v>28.248067753520438</v>
       </c>
       <c r="AR27" t="s">
         <v>252</v>
@@ -9359,16 +9359,16 @@
         <v>437</v>
       </c>
       <c r="BA27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="BB27" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="BC27">
-        <v>0.99560743175223188</v>
+        <v>0.99135720783404546</v>
       </c>
       <c r="BD27">
-        <v>80.530417875749265</v>
+        <v>158.45118970916684</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9433,16 +9433,16 @@
         <v>289</v>
       </c>
       <c r="Y28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="Z28" t="s">
         <v>322</v>
       </c>
       <c r="AA28">
-        <v>0.99749418850407234</v>
+        <v>0.99803201804692143</v>
       </c>
       <c r="AB28">
-        <v>45.939877425340249</v>
+        <v>36.079669139774055</v>
       </c>
       <c r="AD28" t="s">
         <v>252</v>
@@ -9475,10 +9475,10 @@
         <v>402</v>
       </c>
       <c r="AO28">
-        <v>0.99874953222888541</v>
+        <v>0.99882321467857593</v>
       </c>
       <c r="AP28">
-        <v>22.925242470433936</v>
+        <v>21.574397559441575</v>
       </c>
       <c r="AR28" t="s">
         <v>252</v>
@@ -9505,16 +9505,16 @@
         <v>439</v>
       </c>
       <c r="BA28" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="BB28" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="BC28">
-        <v>0.99689089953602861</v>
+        <v>0.98395626279590787</v>
       </c>
       <c r="BD28">
-        <v>57.000175172809875</v>
+        <v>294.13518207502182</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9579,16 +9579,16 @@
         <v>291</v>
       </c>
       <c r="Y29" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="Z29" t="s">
         <v>323</v>
       </c>
       <c r="AA29">
-        <v>0.9992072598548265</v>
+        <v>0.99877722064413432</v>
       </c>
       <c r="AB29">
-        <v>14.533569328180825</v>
+        <v>22.417621524203621</v>
       </c>
       <c r="AD29" t="s">
         <v>252</v>
@@ -9621,10 +9621,10 @@
         <v>404</v>
       </c>
       <c r="AO29">
-        <v>0.99831790956100308</v>
+        <v>0.99838829169023302</v>
       </c>
       <c r="AP29">
-        <v>30.838324714942974</v>
+        <v>29.547985679061497</v>
       </c>
       <c r="AR29" t="s">
         <v>252</v>
@@ -9657,10 +9657,10 @@
         <v>479</v>
       </c>
       <c r="BC29">
-        <v>0.99657569928293988</v>
+        <v>0.98404695622985239</v>
       </c>
       <c r="BD29">
-        <v>62.778846479435288</v>
+        <v>292.47246911937344</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9725,16 +9725,16 @@
         <v>293</v>
       </c>
       <c r="Y30" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="Z30" t="s">
         <v>324</v>
       </c>
       <c r="AA30">
-        <v>0.99803201804692143</v>
+        <v>0.99600892100673577</v>
       </c>
       <c r="AB30">
-        <v>36.079669139774055</v>
+        <v>73.169781543177265</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9799,16 +9799,16 @@
         <v>295</v>
       </c>
       <c r="Y31" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="Z31" t="s">
         <v>325</v>
       </c>
       <c r="AA31">
-        <v>0.99837547744095589</v>
+        <v>0.99886825748232866</v>
       </c>
       <c r="AB31">
-        <v>29.782913582475086</v>
+        <v>20.748612823974995</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9873,16 +9873,16 @@
         <v>297</v>
       </c>
       <c r="Y32" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="Z32" t="s">
         <v>326</v>
       </c>
       <c r="AA32">
-        <v>0.99748803033916245</v>
+        <v>0.99839748836760267</v>
       </c>
       <c r="AB32">
-        <v>46.052777115354985</v>
+        <v>29.37937992728429</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9947,16 +9947,16 @@
         <v>299</v>
       </c>
       <c r="Y33" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="Z33" t="s">
         <v>327</v>
       </c>
       <c r="AA33">
-        <v>0.99736118721915257</v>
+        <v>0.99837547744095589</v>
       </c>
       <c r="AB33">
-        <v>48.378234315535408</v>
+        <v>29.782913582475086</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -10021,16 +10021,16 @@
         <v>301</v>
       </c>
       <c r="Y34" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="Z34" t="s">
         <v>328</v>
       </c>
       <c r="AA34">
-        <v>0.99856694466146878</v>
+        <v>0.99748803033916245</v>
       </c>
       <c r="AB34">
-        <v>26.272681206405</v>
+        <v>46.052777115354985</v>
       </c>
     </row>
   </sheetData>
@@ -10039,7 +10039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F40BF757-D049-4810-90CE-90EDE88989C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD920A58-8B84-4666-88DF-315D218E0ACA}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10151,7 +10151,7 @@
         <v>480</v>
       </c>
       <c r="K11" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="L11">
         <v>7.7363165779076795</v>
@@ -10184,7 +10184,7 @@
         <v>518</v>
       </c>
       <c r="X11" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="Y11">
         <v>39.450749999999999</v>
@@ -10219,7 +10219,7 @@
         <v>482</v>
       </c>
       <c r="K12" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="L12">
         <v>2.3427652611420688</v>
@@ -10252,7 +10252,7 @@
         <v>520</v>
       </c>
       <c r="X12" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="Y12">
         <v>10.7745</v>
@@ -10287,7 +10287,7 @@
         <v>484</v>
       </c>
       <c r="K13" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="L13">
         <v>21.492626448742886</v>
@@ -10320,7 +10320,7 @@
         <v>522</v>
       </c>
       <c r="X13" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
       <c r="Y13">
         <v>38.600250000000003</v>
@@ -10355,7 +10355,7 @@
         <v>486</v>
       </c>
       <c r="K14" t="s">
-        <v>397</v>
+        <v>381</v>
       </c>
       <c r="L14">
         <v>6.3986137173550848</v>
@@ -10388,7 +10388,7 @@
         <v>524</v>
       </c>
       <c r="X14" t="s">
-        <v>476</v>
+        <v>451</v>
       </c>
       <c r="Y14">
         <v>4.0402500000000003</v>
@@ -10423,7 +10423,7 @@
         <v>488</v>
       </c>
       <c r="K15" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
       <c r="L15">
         <v>4.0537250245901548</v>
@@ -10456,7 +10456,7 @@
         <v>526</v>
       </c>
       <c r="X15" t="s">
-        <v>478</v>
+        <v>453</v>
       </c>
       <c r="Y15">
         <v>39.321750000000002</v>
@@ -10491,7 +10491,7 @@
         <v>490</v>
       </c>
       <c r="K16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L16">
         <v>9.6185391844194168</v>
@@ -10524,7 +10524,7 @@
         <v>528</v>
       </c>
       <c r="X16" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Y16">
         <v>12.592499999999999</v>
@@ -10592,7 +10592,7 @@
         <v>530</v>
       </c>
       <c r="X17" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="Y17">
         <v>15.871499999999999</v>
@@ -10627,7 +10627,7 @@
         <v>494</v>
       </c>
       <c r="K18" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="L18">
         <v>4.7225970155809494</v>
@@ -10660,7 +10660,7 @@
         <v>532</v>
       </c>
       <c r="X18" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="Y18">
         <v>19.04175</v>
@@ -10728,7 +10728,7 @@
         <v>534</v>
       </c>
       <c r="X19" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="Y19">
         <v>28.344000000000001</v>
@@ -10763,7 +10763,7 @@
         <v>498</v>
       </c>
       <c r="K20" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="L20">
         <v>10.618766499150132</v>
@@ -10796,7 +10796,7 @@
         <v>536</v>
       </c>
       <c r="X20" t="s">
-        <v>472</v>
+        <v>443</v>
       </c>
       <c r="Y20">
         <v>14.163</v>
@@ -10831,7 +10831,7 @@
         <v>500</v>
       </c>
       <c r="K21" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
       <c r="L21">
         <v>37.276481001553563</v>
@@ -10864,7 +10864,7 @@
         <v>538</v>
       </c>
       <c r="X21" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="Y21">
         <v>2.0775000000000001</v>
@@ -10899,7 +10899,7 @@
         <v>502</v>
       </c>
       <c r="K22" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="L22">
         <v>20.90644030096918</v>
@@ -10932,7 +10932,7 @@
         <v>540</v>
       </c>
       <c r="X22" t="s">
-        <v>457</v>
+        <v>471</v>
       </c>
       <c r="Y22">
         <v>9.2415000000000003</v>
@@ -11000,7 +11000,7 @@
         <v>542</v>
       </c>
       <c r="X23" t="s">
-        <v>445</v>
+        <v>465</v>
       </c>
       <c r="Y23">
         <v>0.97650000000000003</v>
@@ -11035,7 +11035,7 @@
         <v>506</v>
       </c>
       <c r="K24" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L24">
         <v>3.655060122103603</v>
@@ -11068,7 +11068,7 @@
         <v>544</v>
       </c>
       <c r="X24" t="s">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="Y24">
         <v>6.8857499999999998</v>
@@ -11103,7 +11103,7 @@
         <v>508</v>
       </c>
       <c r="K25" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="L25">
         <v>48.450394178145253</v>
@@ -11136,7 +11136,7 @@
         <v>546</v>
       </c>
       <c r="X25" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="Y25">
         <v>71.778000000000006</v>
@@ -11204,7 +11204,7 @@
         <v>548</v>
       </c>
       <c r="X26" t="s">
-        <v>443</v>
+        <v>463</v>
       </c>
       <c r="Y26">
         <v>40.861499999999999</v>
@@ -11239,7 +11239,7 @@
         <v>512</v>
       </c>
       <c r="K27" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="L27">
         <v>23.13749613808001</v>
@@ -11272,7 +11272,7 @@
         <v>550</v>
       </c>
       <c r="X27" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="Y27">
         <v>53.390250000000002</v>
@@ -11307,7 +11307,7 @@
         <v>514</v>
       </c>
       <c r="K28" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
       <c r="L28">
         <v>6.7463178806119855</v>
@@ -11340,7 +11340,7 @@
         <v>552</v>
       </c>
       <c r="X28" t="s">
-        <v>451</v>
+        <v>477</v>
       </c>
       <c r="Y28">
         <v>49.423499999999997</v>
@@ -11408,7 +11408,7 @@
         <v>554</v>
       </c>
       <c r="X29" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="Y29">
         <v>48.613500000000002</v>
@@ -11423,7 +11423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416A00D7-2254-4673-AB4B-76218A5873B7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A036054F-2B45-46AD-A2C8-44BC4ACEC264}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13240,7 +13240,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825EF5CC-63CB-4693-9676-4491F9A86A3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{511F5A09-5A6F-44AD-A847-4AFF88ADC352}">
   <dimension ref="B2:M15"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
